--- a/predicciones.xlsx
+++ b/predicciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Proyectos\Tabla mundial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C3F4FA9-C1CF-42A7-AD63-0B4A8F753BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{381A51F2-783E-4E3B-A92F-9AFA0AB804B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2234" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="144">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -453,9 +453,6 @@
   </si>
   <si>
     <t>luchodela121998@gmail.com</t>
-  </si>
-  <si>
-    <t>Ernesto Lopez</t>
   </si>
   <si>
     <t>Respuestas</t>
@@ -582,7 +579,42 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="15">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -667,10 +699,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="9"/>
-      <tableStyleElement type="headerRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="secondRowStripe" dxfId="6"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="14"/>
+      <tableStyleElement type="headerRow" dxfId="13"/>
+      <tableStyleElement type="firstRowStripe" dxfId="12"/>
+      <tableStyleElement type="secondRowStripe" dxfId="11"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -766,10 +798,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="5">
+    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="10">
       <calculatedColumnFormula>SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="4">
+    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="9">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1266,10 +1298,10 @@
         <v>74</v>
       </c>
       <c r="BX1" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="BY1" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="BY1" s="4" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:77" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1280,7 +1312,7 @@
         <v>75</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>76</v>
@@ -1500,7 +1532,7 @@
       </c>
       <c r="BX2" s="5">
         <f t="shared" ref="BX2:BX14" si="0">SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BY2" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -1515,7 +1547,7 @@
         <v>75</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>77</v>
@@ -1750,7 +1782,7 @@
         <v>75</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>77</v>
@@ -1985,7 +2017,7 @@
         <v>75</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>76</v>
@@ -2205,7 +2237,7 @@
       </c>
       <c r="BX5" s="5">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BY5" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2220,7 +2252,7 @@
         <v>75</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>77</v>
@@ -2455,7 +2487,7 @@
         <v>75</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>77</v>
@@ -2690,7 +2722,7 @@
         <v>121</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>77</v>
@@ -2925,7 +2957,7 @@
         <v>123</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>77</v>
@@ -3160,7 +3192,7 @@
         <v>123</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>77</v>
@@ -3395,7 +3427,7 @@
         <v>123</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>77</v>
@@ -3630,7 +3662,7 @@
         <v>126</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>76</v>
@@ -3865,7 +3897,7 @@
         <v>75</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>76</v>
@@ -4100,7 +4132,7 @@
         <v>75</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>76</v>
@@ -4332,7 +4364,7 @@
         <v>46186.93277777778</v>
       </c>
       <c r="C15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D15" t="s">
         <v>77</v>
@@ -4565,7 +4597,7 @@
     </row>
     <row r="18" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D18" t="s">
         <v>77</v>
@@ -4574,6 +4606,9 @@
         <v>92</v>
       </c>
       <c r="J18" t="s">
+        <v>76</v>
+      </c>
+      <c r="K18" t="s">
         <v>76</v>
       </c>
       <c r="V18" t="s">
@@ -4582,23 +4617,28 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D16">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="5" operator="equal">
       <formula>$D$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E16">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
       <formula>$E$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J16">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
       <formula>$J$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V16">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+      <formula>$V$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$V$18</formula>
+      <formula>$K$18</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/predicciones.xlsx
+++ b/predicciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Proyectos\Tabla mundial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{381A51F2-783E-4E3B-A92F-9AFA0AB804B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A1AA2C-B468-4AA9-8A88-AA01019C3043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="144">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -579,7 +579,21 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -699,10 +713,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="14"/>
-      <tableStyleElement type="headerRow" dxfId="13"/>
-      <tableStyleElement type="firstRowStripe" dxfId="12"/>
-      <tableStyleElement type="secondRowStripe" dxfId="11"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="secondRowStripe" dxfId="13"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -798,10 +812,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="10">
+    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="12">
       <calculatedColumnFormula>SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="9">
+    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="11">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2472,7 +2486,7 @@
       </c>
       <c r="BX6" s="5">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BY6" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2942,7 +2956,7 @@
       </c>
       <c r="BX8" s="5">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BY8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3177,7 +3191,7 @@
       </c>
       <c r="BX9" s="5">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BY9" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3647,7 +3661,7 @@
       </c>
       <c r="BX11" s="5">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BY11" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4117,7 +4131,7 @@
       </c>
       <c r="BX13" s="5">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BY13" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4611,34 +4625,42 @@
       <c r="K18" t="s">
         <v>76</v>
       </c>
+      <c r="P18" t="s">
+        <v>76</v>
+      </c>
       <c r="V18" t="s">
         <v>101</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D16">
-    <cfRule type="cellIs" dxfId="8" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
       <formula>$D$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E16">
-    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">
       <formula>$E$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J16">
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
       <formula>$J$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K15">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+      <formula>$K$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="V2:V16">
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
       <formula>$V$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K15">
+  <conditionalFormatting sqref="P2:P15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$K$18</formula>
+      <formula>$P$18</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/predicciones.xlsx
+++ b/predicciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Proyectos\Tabla mundial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A1AA2C-B468-4AA9-8A88-AA01019C3043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF4BC32-FFEE-4A1D-9332-91CCE6EB9F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="144">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -513,7 +513,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -524,6 +524,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -553,7 +560,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -575,11 +582,222 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="47">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -713,10 +931,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="secondRowStripe" dxfId="13"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="46"/>
+      <tableStyleElement type="headerRow" dxfId="45"/>
+      <tableStyleElement type="firstRowStripe" dxfId="44"/>
+      <tableStyleElement type="secondRowStripe" dxfId="43"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -812,10 +1030,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="12">
+    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="42">
       <calculatedColumnFormula>SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="11">
+    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="41">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1546,7 +1764,7 @@
       </c>
       <c r="BX2" s="5">
         <f t="shared" ref="BX2:BX14" si="0">SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BY2" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -1781,7 +1999,7 @@
       </c>
       <c r="BX3" s="5">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BY3" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2016,7 +2234,7 @@
       </c>
       <c r="BX4" s="5">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BY4" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2251,7 +2469,7 @@
       </c>
       <c r="BX5" s="5">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BY5" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2486,7 +2704,7 @@
       </c>
       <c r="BX6" s="5">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BY6" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2721,7 +2939,7 @@
       </c>
       <c r="BX7" s="5">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BY7" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2956,7 +3174,7 @@
       </c>
       <c r="BX8" s="5">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BY8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3191,7 +3409,7 @@
       </c>
       <c r="BX9" s="5">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BY9" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3426,7 +3644,7 @@
       </c>
       <c r="BX10" s="5">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BY10" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3661,7 +3879,7 @@
       </c>
       <c r="BX11" s="5">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BY11" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3896,7 +4114,7 @@
       </c>
       <c r="BX12" s="5">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BY12" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4131,7 +4349,7 @@
       </c>
       <c r="BX13" s="5">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BY13" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4366,7 +4584,7 @@
       </c>
       <c r="BX14" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY14" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4598,7 +4816,7 @@
       </c>
       <c r="BX15" s="7">
         <f>SUMPRODUCT((D15:BW15=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BY15" s="8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4609,7 +4827,7 @@
       <c r="BX16" s="7"/>
       <c r="BY16" s="8"/>
     </row>
-    <row r="18" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>127</v>
       </c>
@@ -4628,39 +4846,71 @@
       <c r="P18" t="s">
         <v>76</v>
       </c>
+      <c r="Q18" t="s">
+        <v>99</v>
+      </c>
       <c r="V18" t="s">
         <v>101</v>
+      </c>
+      <c r="W18" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB18" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH18" s="9" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D16">
-    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="10" operator="equal">
       <formula>$D$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E16">
-    <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="9" operator="equal">
       <formula>$E$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J16">
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="8" operator="equal">
       <formula>$J$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K15">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="6" operator="equal">
       <formula>$K$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P15">
+    <cfRule type="cellIs" dxfId="14" priority="5" operator="equal">
+      <formula>$P$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="V2:V16">
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
       <formula>$V$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P15">
+  <conditionalFormatting sqref="Q2:Q15">
+    <cfRule type="cellIs" dxfId="12" priority="4" operator="equal">
+      <formula>$Q$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W15">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
+      <formula>$W$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB2:AB15">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+      <formula>$AB$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH2:AH15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$P$18</formula>
+      <formula>$AH$18</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/predicciones.xlsx
+++ b/predicciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Proyectos\Tabla mundial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF4BC32-FFEE-4A1D-9332-91CCE6EB9F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30FEB3D1-8EB2-4736-A2EB-B6365AA03298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="144">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -587,147 +587,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="47">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="27">
     <dxf>
       <fill>
         <patternFill>
@@ -931,10 +791,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="46"/>
-      <tableStyleElement type="headerRow" dxfId="45"/>
-      <tableStyleElement type="firstRowStripe" dxfId="44"/>
-      <tableStyleElement type="secondRowStripe" dxfId="43"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="26"/>
+      <tableStyleElement type="headerRow" dxfId="25"/>
+      <tableStyleElement type="firstRowStripe" dxfId="24"/>
+      <tableStyleElement type="secondRowStripe" dxfId="23"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1030,10 +890,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="42">
+    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="22">
       <calculatedColumnFormula>SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="41">
+    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="21">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1999,7 +1859,7 @@
       </c>
       <c r="BX3" s="5">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BY3" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2939,7 +2799,7 @@
       </c>
       <c r="BX7" s="5">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BY7" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3879,7 +3739,7 @@
       </c>
       <c r="BX11" s="5">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BY11" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4816,7 +4676,7 @@
       </c>
       <c r="BX15" s="7">
         <f>SUMPRODUCT((D15:BW15=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BY15" s="8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4858,59 +4718,67 @@
       <c r="AB18" s="9" t="s">
         <v>80</v>
       </c>
+      <c r="AC18" t="s">
+        <v>102</v>
+      </c>
       <c r="AH18" s="9" t="s">
         <v>76</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D16">
-    <cfRule type="cellIs" dxfId="18" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="11" operator="equal">
       <formula>$D$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E16">
-    <cfRule type="cellIs" dxfId="17" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="10" operator="equal">
       <formula>$E$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J16">
-    <cfRule type="cellIs" dxfId="16" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="9" operator="equal">
       <formula>$J$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K15">
-    <cfRule type="cellIs" dxfId="15" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="7" operator="equal">
       <formula>$K$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P15">
-    <cfRule type="cellIs" dxfId="14" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="6" operator="equal">
       <formula>$P$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="Q2:Q15">
+    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
+      <formula>$Q$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="V2:V16">
-    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="8" operator="equal">
       <formula>$V$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q15">
-    <cfRule type="cellIs" dxfId="12" priority="4" operator="equal">
-      <formula>$Q$18</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="W2:W15">
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="4" operator="equal">
       <formula>$W$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB15">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
       <formula>$AB$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH15">
+    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
+      <formula>$AH$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC2:AC15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$AH$18</formula>
+      <formula>$AC$18</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/predicciones.xlsx
+++ b/predicciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Proyectos\Tabla mundial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30FEB3D1-8EB2-4736-A2EB-B6365AA03298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2251C9-1D23-4B21-8524-05E0C23E2BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1125" uniqueCount="144">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -587,70 +587,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="18">
     <dxf>
       <fill>
         <patternFill>
@@ -791,10 +728,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="26"/>
-      <tableStyleElement type="headerRow" dxfId="25"/>
-      <tableStyleElement type="firstRowStripe" dxfId="24"/>
-      <tableStyleElement type="secondRowStripe" dxfId="23"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="17"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="secondRowStripe" dxfId="14"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -890,10 +827,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="22">
+    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="13">
       <calculatedColumnFormula>SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="21">
+    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="12">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1859,7 +1796,7 @@
       </c>
       <c r="BX3" s="5">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BY3" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2094,7 +2031,7 @@
       </c>
       <c r="BX4" s="5">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BY4" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2799,7 +2736,7 @@
       </c>
       <c r="BX7" s="5">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BY7" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3034,7 +2971,7 @@
       </c>
       <c r="BX8" s="5">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BY8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3504,7 +3441,7 @@
       </c>
       <c r="BX10" s="5">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BY10" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3974,7 +3911,7 @@
       </c>
       <c r="BX12" s="5">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BY12" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4676,7 +4613,7 @@
       </c>
       <c r="BX15" s="7">
         <f>SUMPRODUCT((D15:BW15=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BY15" s="8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4687,7 +4624,7 @@
       <c r="BX16" s="7"/>
       <c r="BY16" s="8"/>
     </row>
-    <row r="18" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>127</v>
       </c>
@@ -4723,62 +4660,70 @@
       </c>
       <c r="AH18" s="9" t="s">
         <v>76</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D16">
-    <cfRule type="cellIs" dxfId="20" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
       <formula>$D$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E16">
-    <cfRule type="cellIs" dxfId="19" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
       <formula>$E$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J16">
-    <cfRule type="cellIs" dxfId="18" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
       <formula>$J$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K15">
-    <cfRule type="cellIs" dxfId="17" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
       <formula>$K$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P15">
-    <cfRule type="cellIs" dxfId="16" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
       <formula>$P$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q15">
-    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>$Q$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V16">
-    <cfRule type="cellIs" dxfId="14" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="9" operator="equal">
       <formula>$V$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W15">
-    <cfRule type="cellIs" dxfId="13" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>$W$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB15">
-    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>$AB$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AC2:AC15">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+      <formula>$AC$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH15">
-    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>$AH$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC2:AC15">
+  <conditionalFormatting sqref="AI2:AI15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$AC$18</formula>
+      <formula>$AI$18</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/predicciones.xlsx
+++ b/predicciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Proyectos\Tabla mundial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2251C9-1D23-4B21-8524-05E0C23E2BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{243B7DA5-BA56-42FA-A7AD-367A935BAA45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1125" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="144">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -587,7 +587,14 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="19">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -728,10 +735,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="17"/>
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="firstRowStripe" dxfId="15"/>
-      <tableStyleElement type="secondRowStripe" dxfId="14"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="18"/>
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="firstRowStripe" dxfId="16"/>
+      <tableStyleElement type="secondRowStripe" dxfId="15"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -827,10 +834,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="13">
+    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="14">
       <calculatedColumnFormula>SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="12">
+    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="13">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1561,7 +1568,7 @@
       </c>
       <c r="BX2" s="5">
         <f t="shared" ref="BX2:BX14" si="0">SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BY2" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4624,7 +4631,7 @@
       <c r="BX16" s="7"/>
       <c r="BY16" s="8"/>
     </row>
-    <row r="18" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>127</v>
       </c>
@@ -4663,67 +4670,75 @@
       </c>
       <c r="AI18" t="s">
         <v>103</v>
+      </c>
+      <c r="AT18" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D16">
-    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="13" operator="equal">
       <formula>$D$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E16">
-    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
       <formula>$E$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J16">
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
       <formula>$J$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K15">
-    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="9" operator="equal">
       <formula>$K$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P15">
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
       <formula>$P$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q15">
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
       <formula>$Q$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V16">
-    <cfRule type="cellIs" dxfId="5" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
       <formula>$V$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W15">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
       <formula>$W$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB15">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>$AB$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC15">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>$AC$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH15">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>$AH$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI15">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>$AI$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AT2:AT15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$AI$18</formula>
+      <formula>$AT$18</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/predicciones.xlsx
+++ b/predicciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Proyectos\Tabla mundial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{243B7DA5-BA56-42FA-A7AD-367A935BAA45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F537FA28-B6ED-4EE2-BD6B-C00F5AE82631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="144">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -587,7 +587,210 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="48">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -735,10 +938,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="18"/>
-      <tableStyleElement type="headerRow" dxfId="17"/>
-      <tableStyleElement type="firstRowStripe" dxfId="16"/>
-      <tableStyleElement type="secondRowStripe" dxfId="15"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="47"/>
+      <tableStyleElement type="headerRow" dxfId="46"/>
+      <tableStyleElement type="firstRowStripe" dxfId="45"/>
+      <tableStyleElement type="secondRowStripe" dxfId="44"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -834,10 +1037,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="14">
+    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="43">
       <calculatedColumnFormula>SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="13">
+    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="42">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1568,7 +1771,7 @@
       </c>
       <c r="BX2" s="5">
         <f t="shared" ref="BX2:BX14" si="0">SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BY2" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2743,7 +2946,7 @@
       </c>
       <c r="BX7" s="5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BY7" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2978,7 +3181,7 @@
       </c>
       <c r="BX8" s="5">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BY8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3918,7 +4121,7 @@
       </c>
       <c r="BX12" s="5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BY12" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4153,7 +4356,7 @@
       </c>
       <c r="BX13" s="5">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BY13" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4631,7 +4834,7 @@
       <c r="BX16" s="7"/>
       <c r="BY16" s="8"/>
     </row>
-    <row r="18" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>127</v>
       </c>
@@ -4671,74 +4874,90 @@
       <c r="AI18" t="s">
         <v>103</v>
       </c>
+      <c r="AN18" s="9" t="s">
+        <v>76</v>
+      </c>
       <c r="AT18" t="s">
+        <v>76</v>
+      </c>
+      <c r="AU18" t="s">
         <v>76</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D16">
-    <cfRule type="cellIs" dxfId="12" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="15" operator="equal">
       <formula>$D$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E16">
-    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="14" operator="equal">
       <formula>$E$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J16">
-    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="13" operator="equal">
       <formula>$J$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K15">
-    <cfRule type="cellIs" dxfId="9" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="11" operator="equal">
       <formula>$K$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P15">
-    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="10" operator="equal">
       <formula>$P$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q15">
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="9" operator="equal">
       <formula>$Q$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V16">
-    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="12" operator="equal">
       <formula>$V$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W15">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="8" operator="equal">
       <formula>$W$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB15">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="7" operator="equal">
       <formula>$AB$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC15">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="5" operator="equal">
       <formula>$AC$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH15">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="6" operator="equal">
       <formula>$AH$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI15">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="4" operator="equal">
       <formula>$AI$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT15">
+    <cfRule type="cellIs" dxfId="16" priority="3" operator="equal">
+      <formula>$AT$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AU2:AU15">
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="equal">
+      <formula>$AU$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AN2:AN15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$AT$18</formula>
+      <formula>$AN$18</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/predicciones.xlsx
+++ b/predicciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Proyectos\Tabla mundial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F537FA28-B6ED-4EE2-BD6B-C00F5AE82631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71B1353F-E3FF-465A-9025-E34D9B1AF87E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="144">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -587,84 +587,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="48">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="37">
     <dxf>
       <fill>
         <patternFill>
@@ -938,10 +861,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="47"/>
-      <tableStyleElement type="headerRow" dxfId="46"/>
-      <tableStyleElement type="firstRowStripe" dxfId="45"/>
-      <tableStyleElement type="secondRowStripe" dxfId="44"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="36"/>
+      <tableStyleElement type="headerRow" dxfId="35"/>
+      <tableStyleElement type="firstRowStripe" dxfId="34"/>
+      <tableStyleElement type="secondRowStripe" dxfId="33"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1037,10 +960,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="43">
+    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="32">
       <calculatedColumnFormula>SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="42">
+    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="31">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1771,7 +1694,7 @@
       </c>
       <c r="BX2" s="5">
         <f t="shared" ref="BX2:BX14" si="0">SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BY2" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2946,7 +2869,7 @@
       </c>
       <c r="BX7" s="5">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BY7" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4121,7 +4044,7 @@
       </c>
       <c r="BX12" s="5">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BY12" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4877,6 +4800,9 @@
       <c r="AN18" s="9" t="s">
         <v>76</v>
       </c>
+      <c r="AO18" t="s">
+        <v>76</v>
+      </c>
       <c r="AT18" t="s">
         <v>76</v>
       </c>
@@ -4886,78 +4812,83 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D16">
-    <cfRule type="cellIs" dxfId="28" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="16" operator="equal">
       <formula>$D$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E16">
-    <cfRule type="cellIs" dxfId="27" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="15" operator="equal">
       <formula>$E$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J16">
-    <cfRule type="cellIs" dxfId="26" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="14" operator="equal">
       <formula>$J$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K15">
-    <cfRule type="cellIs" dxfId="25" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="12" operator="equal">
       <formula>$K$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P15">
-    <cfRule type="cellIs" dxfId="24" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="11" operator="equal">
       <formula>$P$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q15">
-    <cfRule type="cellIs" dxfId="23" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="10" operator="equal">
       <formula>$Q$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V16">
-    <cfRule type="cellIs" dxfId="22" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="13" operator="equal">
       <formula>$V$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W15">
-    <cfRule type="cellIs" dxfId="21" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="9" operator="equal">
       <formula>$W$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB15">
-    <cfRule type="cellIs" dxfId="20" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="8" operator="equal">
       <formula>$AB$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC15">
-    <cfRule type="cellIs" dxfId="19" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="6" operator="equal">
       <formula>$AC$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH15">
-    <cfRule type="cellIs" dxfId="18" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="7" operator="equal">
       <formula>$AH$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI15">
-    <cfRule type="cellIs" dxfId="17" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="5" operator="equal">
       <formula>$AI$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AN2:AN15">
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
+      <formula>$AN$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT15">
-    <cfRule type="cellIs" dxfId="16" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="4" operator="equal">
       <formula>$AT$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU15">
-    <cfRule type="cellIs" dxfId="15" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="3" operator="equal">
       <formula>$AU$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AN2:AN15">
+  <conditionalFormatting sqref="AO2:AO15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$AN$18</formula>
+      <formula>$AO$18</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/predicciones.xlsx
+++ b/predicciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Proyectos\Tabla mundial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71B1353F-E3FF-465A-9025-E34D9B1AF87E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19D84A7B-C56E-4D15-A2AB-95D672098C3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="145">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -504,6 +504,9 @@
   </si>
   <si>
     <t xml:space="preserve">Ernesto </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -587,7 +590,567 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="37">
+  <dxfs count="117">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -861,10 +1424,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="36"/>
-      <tableStyleElement type="headerRow" dxfId="35"/>
-      <tableStyleElement type="firstRowStripe" dxfId="34"/>
-      <tableStyleElement type="secondRowStripe" dxfId="33"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="116"/>
+      <tableStyleElement type="headerRow" dxfId="115"/>
+      <tableStyleElement type="firstRowStripe" dxfId="114"/>
+      <tableStyleElement type="secondRowStripe" dxfId="113"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -960,10 +1523,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="32">
+    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="112">
       <calculatedColumnFormula>SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="31">
+    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="111">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1588,7 +2151,7 @@
         <v>76</v>
       </c>
       <c r="AO2" s="3" t="s">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="AP2" s="3" t="s">
         <v>83</v>
@@ -1694,7 +2257,7 @@
       </c>
       <c r="BX2" s="5">
         <f t="shared" ref="BX2:BX14" si="0">SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BY2" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -1929,7 +2492,7 @@
       </c>
       <c r="BX3" s="5">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BY3" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2164,7 +2727,7 @@
       </c>
       <c r="BX4" s="5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BY4" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2399,7 +2962,7 @@
       </c>
       <c r="BX5" s="5">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BY5" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2634,7 +3197,7 @@
       </c>
       <c r="BX6" s="5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BY6" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2869,7 +3432,7 @@
       </c>
       <c r="BX7" s="5">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BY7" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3104,7 +3667,7 @@
       </c>
       <c r="BX8" s="5">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BY8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3339,7 +3902,7 @@
       </c>
       <c r="BX9" s="5">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BY9" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3574,7 +4137,7 @@
       </c>
       <c r="BX10" s="5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BY10" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3809,7 +4372,7 @@
       </c>
       <c r="BX11" s="5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BY11" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4044,7 +4607,7 @@
       </c>
       <c r="BX12" s="5">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BY12" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4279,7 +4842,7 @@
       </c>
       <c r="BX13" s="5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BY13" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4514,7 +5077,7 @@
       </c>
       <c r="BX14" s="5">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BY14" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4746,7 +5309,7 @@
       </c>
       <c r="BX15" s="7">
         <f>SUMPRODUCT((D15:BW15=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BY15" s="8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4757,7 +5320,7 @@
       <c r="BX16" s="7"/>
       <c r="BY16" s="8"/>
     </row>
-    <row r="18" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>127</v>
       </c>
@@ -4807,88 +5370,128 @@
         <v>76</v>
       </c>
       <c r="AU18" t="s">
+        <v>76</v>
+      </c>
+      <c r="AZ18" t="s">
+        <v>85</v>
+      </c>
+      <c r="BA18" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="BF18" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="BG18" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="BL18" s="9" t="s">
         <v>76</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D16">
-    <cfRule type="cellIs" dxfId="30" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="21" operator="equal">
       <formula>$D$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E16">
-    <cfRule type="cellIs" dxfId="29" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="20" operator="equal">
       <formula>$E$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J16">
-    <cfRule type="cellIs" dxfId="28" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="19" operator="equal">
       <formula>$J$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K15">
-    <cfRule type="cellIs" dxfId="27" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="17" operator="equal">
       <formula>$K$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P15">
-    <cfRule type="cellIs" dxfId="26" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="16" operator="equal">
       <formula>$P$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q15">
-    <cfRule type="cellIs" dxfId="25" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="15" operator="equal">
       <formula>$Q$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V16">
-    <cfRule type="cellIs" dxfId="24" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="18" operator="equal">
       <formula>$V$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W15">
-    <cfRule type="cellIs" dxfId="23" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="14" operator="equal">
       <formula>$W$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB15">
-    <cfRule type="cellIs" dxfId="22" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="13" operator="equal">
       <formula>$AB$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC15">
-    <cfRule type="cellIs" dxfId="21" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="11" operator="equal">
       <formula>$AC$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH15">
-    <cfRule type="cellIs" dxfId="20" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="12" operator="equal">
       <formula>$AH$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI15">
-    <cfRule type="cellIs" dxfId="19" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="10" operator="equal">
       <formula>$AI$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN15">
-    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="7" operator="equal">
       <formula>$AN$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AO2:AO15">
+    <cfRule type="cellIs" dxfId="27" priority="6" operator="equal">
+      <formula>$AO$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT15">
-    <cfRule type="cellIs" dxfId="17" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="9" operator="equal">
       <formula>$AT$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU15">
-    <cfRule type="cellIs" dxfId="16" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="8" operator="equal">
       <formula>$AU$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AO2:AO15">
+  <conditionalFormatting sqref="AZ2:AZ15">
+    <cfRule type="cellIs" dxfId="24" priority="5" operator="equal">
+      <formula>$AZ$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BA2:BA15">
+    <cfRule type="cellIs" dxfId="23" priority="4" operator="equal">
+      <formula>$BA$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BF2:BF15">
+    <cfRule type="cellIs" dxfId="22" priority="3" operator="equal">
+      <formula>$BF$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BG2:BG15">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
+      <formula>$BG$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BL2:BL15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$AO$18</formula>
+      <formula>$BL$18</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/predicciones.xlsx
+++ b/predicciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Proyectos\Tabla mundial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19D84A7B-C56E-4D15-A2AB-95D672098C3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B0AC1A7-AF19-4344-B5E4-DF4B673BAF75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="145">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -590,7 +590,161 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="117">
+  <dxfs count="139">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1424,10 +1578,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="116"/>
-      <tableStyleElement type="headerRow" dxfId="115"/>
-      <tableStyleElement type="firstRowStripe" dxfId="114"/>
-      <tableStyleElement type="secondRowStripe" dxfId="113"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="138"/>
+      <tableStyleElement type="headerRow" dxfId="137"/>
+      <tableStyleElement type="firstRowStripe" dxfId="136"/>
+      <tableStyleElement type="secondRowStripe" dxfId="135"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1523,10 +1677,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="112">
+    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="134">
       <calculatedColumnFormula>SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="111">
+    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="133">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2492,7 +2646,7 @@
       </c>
       <c r="BX3" s="5">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BY3" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2962,7 +3116,7 @@
       </c>
       <c r="BX5" s="5">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BY5" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3197,7 +3351,7 @@
       </c>
       <c r="BX6" s="5">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BY6" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3432,7 +3586,7 @@
       </c>
       <c r="BX7" s="5">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BY7" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3667,7 +3821,7 @@
       </c>
       <c r="BX8" s="5">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BY8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4137,7 +4291,7 @@
       </c>
       <c r="BX10" s="5">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BY10" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4607,7 +4761,7 @@
       </c>
       <c r="BX12" s="5">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BY12" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5309,7 +5463,7 @@
       </c>
       <c r="BX15" s="7">
         <f>SUMPRODUCT((D15:BW15=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BY15" s="8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5320,7 +5474,7 @@
       <c r="BX16" s="7"/>
       <c r="BY16" s="8"/>
     </row>
-    <row r="18" spans="1:64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>127</v>
       </c>
@@ -5386,112 +5540,120 @@
       </c>
       <c r="BL18" s="9" t="s">
         <v>76</v>
+      </c>
+      <c r="BR18" s="9" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D16">
-    <cfRule type="cellIs" dxfId="40" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="22" operator="equal">
       <formula>$D$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E16">
-    <cfRule type="cellIs" dxfId="39" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="21" operator="equal">
       <formula>$E$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J16">
-    <cfRule type="cellIs" dxfId="38" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="20" operator="equal">
       <formula>$J$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K15">
-    <cfRule type="cellIs" dxfId="37" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="18" operator="equal">
       <formula>$K$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P15">
-    <cfRule type="cellIs" dxfId="36" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="17" operator="equal">
       <formula>$P$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q15">
-    <cfRule type="cellIs" dxfId="35" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="16" operator="equal">
       <formula>$Q$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V16">
-    <cfRule type="cellIs" dxfId="34" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="19" operator="equal">
       <formula>$V$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W15">
-    <cfRule type="cellIs" dxfId="33" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="15" operator="equal">
       <formula>$W$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB15">
-    <cfRule type="cellIs" dxfId="32" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="14" operator="equal">
       <formula>$AB$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC15">
-    <cfRule type="cellIs" dxfId="31" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="12" operator="equal">
       <formula>$AC$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH15">
-    <cfRule type="cellIs" dxfId="30" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="13" operator="equal">
       <formula>$AH$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI15">
-    <cfRule type="cellIs" dxfId="29" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="11" operator="equal">
       <formula>$AI$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN15">
-    <cfRule type="cellIs" dxfId="28" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="8" operator="equal">
       <formula>$AN$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO2:AO15">
-    <cfRule type="cellIs" dxfId="27" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="7" operator="equal">
       <formula>$AO$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT15">
-    <cfRule type="cellIs" dxfId="26" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="10" operator="equal">
       <formula>$AT$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU15">
-    <cfRule type="cellIs" dxfId="25" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="9" operator="equal">
       <formula>$AU$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ2:AZ15">
-    <cfRule type="cellIs" dxfId="24" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="6" operator="equal">
       <formula>$AZ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA2:BA15">
-    <cfRule type="cellIs" dxfId="23" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="5" operator="equal">
       <formula>$BA$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BF2:BF15">
-    <cfRule type="cellIs" dxfId="22" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="4" operator="equal">
       <formula>$BF$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG2:BG15">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="3" operator="equal">
       <formula>$BG$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL2:BL15">
+    <cfRule type="cellIs" dxfId="22" priority="2" operator="equal">
+      <formula>$BL$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BR2:BR15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$BL$18</formula>
+      <formula>$BR$18</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/predicciones.xlsx
+++ b/predicciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Proyectos\Tabla mundial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B0AC1A7-AF19-4344-B5E4-DF4B673BAF75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2181074C-631C-4814-A8F9-8492A57B74ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="145">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -590,7 +590,105 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="139">
+  <dxfs count="153">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1578,10 +1676,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="138"/>
-      <tableStyleElement type="headerRow" dxfId="137"/>
-      <tableStyleElement type="firstRowStripe" dxfId="136"/>
-      <tableStyleElement type="secondRowStripe" dxfId="135"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="152"/>
+      <tableStyleElement type="headerRow" dxfId="151"/>
+      <tableStyleElement type="firstRowStripe" dxfId="150"/>
+      <tableStyleElement type="secondRowStripe" dxfId="149"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1677,10 +1775,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="134">
+    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="148">
       <calculatedColumnFormula>SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="133">
+    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="147">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2411,7 +2509,7 @@
       </c>
       <c r="BX2" s="5">
         <f t="shared" ref="BX2:BX14" si="0">SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BY2" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2646,7 +2744,7 @@
       </c>
       <c r="BX3" s="5">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="BY3" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2881,7 +2979,7 @@
       </c>
       <c r="BX4" s="5">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BY4" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3116,7 +3214,7 @@
       </c>
       <c r="BX5" s="5">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BY5" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3351,7 +3449,7 @@
       </c>
       <c r="BX6" s="5">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BY6" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3586,7 +3684,7 @@
       </c>
       <c r="BX7" s="5">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BY7" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3821,7 +3919,7 @@
       </c>
       <c r="BX8" s="5">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BY8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4056,7 +4154,7 @@
       </c>
       <c r="BX9" s="5">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BY9" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4291,7 +4389,7 @@
       </c>
       <c r="BX10" s="5">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BY10" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4526,7 +4624,7 @@
       </c>
       <c r="BX11" s="5">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BY11" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4761,7 +4859,7 @@
       </c>
       <c r="BX12" s="5">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BY12" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4996,7 +5094,7 @@
       </c>
       <c r="BX13" s="5">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BY13" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5231,7 +5329,7 @@
       </c>
       <c r="BX14" s="5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BY14" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5463,7 +5561,7 @@
       </c>
       <c r="BX15" s="7">
         <f>SUMPRODUCT((D15:BW15=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BY15" s="8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5474,7 +5572,7 @@
       <c r="BX16" s="7"/>
       <c r="BY16" s="8"/>
     </row>
-    <row r="18" spans="1:70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>127</v>
       </c>
@@ -5484,11 +5582,20 @@
       <c r="E18" t="s">
         <v>92</v>
       </c>
+      <c r="F18" s="9" t="s">
+        <v>76</v>
+      </c>
       <c r="J18" t="s">
         <v>76</v>
       </c>
       <c r="K18" t="s">
         <v>76</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>95</v>
       </c>
       <c r="P18" t="s">
         <v>76</v>
@@ -5541,119 +5648,150 @@
       <c r="BL18" s="9" t="s">
         <v>76</v>
       </c>
+      <c r="BM18" s="9" t="s">
+        <v>89</v>
+      </c>
       <c r="BR18" s="9" t="s">
         <v>90</v>
+      </c>
+      <c r="BS18" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D16">
-    <cfRule type="cellIs" dxfId="42" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="27" operator="equal">
       <formula>$D$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E16">
-    <cfRule type="cellIs" dxfId="41" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="26" operator="equal">
       <formula>$E$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J16">
-    <cfRule type="cellIs" dxfId="40" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="25" operator="equal">
       <formula>$J$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K15">
-    <cfRule type="cellIs" dxfId="39" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="23" operator="equal">
       <formula>$K$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P15">
-    <cfRule type="cellIs" dxfId="38" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="22" operator="equal">
       <formula>$P$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q15">
-    <cfRule type="cellIs" dxfId="37" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="21" operator="equal">
       <formula>$Q$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V16">
-    <cfRule type="cellIs" dxfId="36" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="24" operator="equal">
       <formula>$V$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W15">
-    <cfRule type="cellIs" dxfId="35" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="20" operator="equal">
       <formula>$W$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB15">
-    <cfRule type="cellIs" dxfId="34" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="19" operator="equal">
       <formula>$AB$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC15">
-    <cfRule type="cellIs" dxfId="33" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="17" operator="equal">
       <formula>$AC$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH15">
-    <cfRule type="cellIs" dxfId="32" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="18" operator="equal">
       <formula>$AH$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI15">
-    <cfRule type="cellIs" dxfId="31" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="16" operator="equal">
       <formula>$AI$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN15">
-    <cfRule type="cellIs" dxfId="30" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="13" operator="equal">
       <formula>$AN$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO2:AO15">
-    <cfRule type="cellIs" dxfId="29" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="12" operator="equal">
       <formula>$AO$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT15">
-    <cfRule type="cellIs" dxfId="28" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="15" operator="equal">
       <formula>$AT$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU15">
-    <cfRule type="cellIs" dxfId="27" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="14" operator="equal">
       <formula>$AU$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ2:AZ15">
-    <cfRule type="cellIs" dxfId="26" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="11" operator="equal">
       <formula>$AZ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA2:BA15">
-    <cfRule type="cellIs" dxfId="25" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="10" operator="equal">
       <formula>$BA$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BF2:BF15">
-    <cfRule type="cellIs" dxfId="24" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="9" operator="equal">
       <formula>$BF$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG2:BG15">
-    <cfRule type="cellIs" dxfId="23" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="8" operator="equal">
       <formula>$BG$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL2:BL15">
-    <cfRule type="cellIs" dxfId="22" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="7" operator="equal">
       <formula>$BL$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BR2:BR15">
+    <cfRule type="cellIs" dxfId="31" priority="6" operator="equal">
+      <formula>$BR$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BS2:BS15">
+    <cfRule type="cellIs" dxfId="30" priority="5" operator="equal">
+      <formula>$BS$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BM2:BM15">
+    <cfRule type="cellIs" dxfId="29" priority="4" operator="equal">
+      <formula>$BM$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F15">
+    <cfRule type="cellIs" dxfId="28" priority="3" operator="equal">
+      <formula>$F$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L15">
+    <cfRule type="cellIs" dxfId="27" priority="2" operator="equal">
+      <formula>$L$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$BR$18</formula>
+      <formula>$M$18</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/predicciones.xlsx
+++ b/predicciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Proyectos\Tabla mundial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2181074C-631C-4814-A8F9-8492A57B74ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{745AD35C-93DD-4264-A7F5-B154932DDD1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="145">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -590,651 +590,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="153">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="61">
     <dxf>
       <fill>
         <patternFill>
@@ -1676,10 +1032,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="152"/>
-      <tableStyleElement type="headerRow" dxfId="151"/>
-      <tableStyleElement type="firstRowStripe" dxfId="150"/>
-      <tableStyleElement type="secondRowStripe" dxfId="149"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="60"/>
+      <tableStyleElement type="headerRow" dxfId="59"/>
+      <tableStyleElement type="firstRowStripe" dxfId="58"/>
+      <tableStyleElement type="secondRowStripe" dxfId="57"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1775,10 +1131,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="148">
+    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="56">
       <calculatedColumnFormula>SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="147">
+    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="55">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2509,7 +1865,7 @@
       </c>
       <c r="BX2" s="5">
         <f t="shared" ref="BX2:BX14" si="0">SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BY2" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2744,7 +2100,7 @@
       </c>
       <c r="BX3" s="5">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BY3" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3214,7 +2570,7 @@
       </c>
       <c r="BX5" s="5">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BY5" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3449,7 +2805,7 @@
       </c>
       <c r="BX6" s="5">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BY6" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3919,7 +3275,7 @@
       </c>
       <c r="BX8" s="5">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BY8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4389,7 +3745,7 @@
       </c>
       <c r="BX10" s="5">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BY10" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4624,7 +3980,7 @@
       </c>
       <c r="BX11" s="5">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BY11" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4859,7 +4215,7 @@
       </c>
       <c r="BX12" s="5">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BY12" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5329,7 +4685,7 @@
       </c>
       <c r="BX14" s="5">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BY14" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5585,6 +4941,9 @@
       <c r="F18" s="9" t="s">
         <v>76</v>
       </c>
+      <c r="G18" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="J18" t="s">
         <v>76</v>
       </c>
@@ -5660,138 +5019,143 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D16">
-    <cfRule type="cellIs" dxfId="52" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="28" operator="equal">
       <formula>$D$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E16">
-    <cfRule type="cellIs" dxfId="51" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="27" operator="equal">
       <formula>$E$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F15">
+    <cfRule type="cellIs" dxfId="52" priority="4" operator="equal">
+      <formula>$F$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J2:J16">
-    <cfRule type="cellIs" dxfId="50" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="26" operator="equal">
       <formula>$J$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K15">
-    <cfRule type="cellIs" dxfId="49" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="24" operator="equal">
       <formula>$K$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L15">
+    <cfRule type="cellIs" dxfId="49" priority="3" operator="equal">
+      <formula>$L$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M15">
+    <cfRule type="cellIs" dxfId="48" priority="2" operator="equal">
+      <formula>$M$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="P2:P15">
-    <cfRule type="cellIs" dxfId="48" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="23" operator="equal">
       <formula>$P$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q15">
-    <cfRule type="cellIs" dxfId="47" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="22" operator="equal">
       <formula>$Q$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V16">
-    <cfRule type="cellIs" dxfId="46" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="25" operator="equal">
       <formula>$V$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W15">
-    <cfRule type="cellIs" dxfId="45" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="21" operator="equal">
       <formula>$W$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB15">
-    <cfRule type="cellIs" dxfId="44" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="20" operator="equal">
       <formula>$AB$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC15">
-    <cfRule type="cellIs" dxfId="43" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="18" operator="equal">
       <formula>$AC$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH15">
-    <cfRule type="cellIs" dxfId="42" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="19" operator="equal">
       <formula>$AH$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI15">
-    <cfRule type="cellIs" dxfId="41" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="17" operator="equal">
       <formula>$AI$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN15">
-    <cfRule type="cellIs" dxfId="40" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="14" operator="equal">
       <formula>$AN$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO2:AO15">
-    <cfRule type="cellIs" dxfId="39" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="13" operator="equal">
       <formula>$AO$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT15">
-    <cfRule type="cellIs" dxfId="38" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="16" operator="equal">
       <formula>$AT$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU15">
-    <cfRule type="cellIs" dxfId="37" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="15" operator="equal">
       <formula>$AU$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ2:AZ15">
-    <cfRule type="cellIs" dxfId="36" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="12" operator="equal">
       <formula>$AZ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA2:BA15">
-    <cfRule type="cellIs" dxfId="35" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="11" operator="equal">
       <formula>$BA$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BF2:BF15">
-    <cfRule type="cellIs" dxfId="34" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="10" operator="equal">
       <formula>$BF$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG2:BG15">
-    <cfRule type="cellIs" dxfId="33" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="9" operator="equal">
       <formula>$BG$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL2:BL15">
-    <cfRule type="cellIs" dxfId="32" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="8" operator="equal">
       <formula>$BL$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="BM2:BM15">
+    <cfRule type="cellIs" dxfId="30" priority="5" operator="equal">
+      <formula>$BM$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="BR2:BR15">
-    <cfRule type="cellIs" dxfId="31" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="7" operator="equal">
       <formula>$BR$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS2:BS15">
-    <cfRule type="cellIs" dxfId="30" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="6" operator="equal">
       <formula>$BS$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BM2:BM15">
-    <cfRule type="cellIs" dxfId="29" priority="4" operator="equal">
-      <formula>$BM$18</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F15">
-    <cfRule type="cellIs" dxfId="28" priority="3" operator="equal">
-      <formula>$F$18</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L15">
-    <cfRule type="cellIs" dxfId="27" priority="2" operator="equal">
-      <formula>$L$18</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M15">
+  <conditionalFormatting sqref="G2:G15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$M$18</formula>
+      <formula>$G$18</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/predicciones.xlsx
+++ b/predicciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User710\Documents\Proyectos\Tabla-mundial-main\Tabla-mundial-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF0333AE-3667-4391-8570-BBDC40E345EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A08E08-5D55-43B3-83B1-1B6183A67D8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="145">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -567,8 +567,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -581,15 +581,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -597,364 +593,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="156">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="105">
     <dxf>
       <fill>
         <patternFill>
@@ -1704,10 +1343,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="155"/>
-      <tableStyleElement type="headerRow" dxfId="154"/>
-      <tableStyleElement type="firstRowStripe" dxfId="153"/>
-      <tableStyleElement type="secondRowStripe" dxfId="152"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="104"/>
+      <tableStyleElement type="headerRow" dxfId="103"/>
+      <tableStyleElement type="firstRowStripe" dxfId="102"/>
+      <tableStyleElement type="secondRowStripe" dxfId="101"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1799,10 +1438,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="151">
+    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="100">
       <calculatedColumnFormula>SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="150">
+    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="99">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2378,7 +2017,7 @@
       <c r="X2" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="Y2" s="10" t="s">
+      <c r="Y2" s="8" t="s">
         <v>79</v>
       </c>
       <c r="Z2" s="3" t="s">
@@ -2533,7 +2172,7 @@
       </c>
       <c r="BX2" s="5">
         <f t="shared" ref="BX2:BX14" si="0">SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BY2" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2768,7 +2407,7 @@
       </c>
       <c r="BX3" s="5">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BY3" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3003,7 +2642,7 @@
       </c>
       <c r="BX4" s="5">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BY4" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3238,7 +2877,7 @@
       </c>
       <c r="BX5" s="5">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BY5" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3708,7 +3347,7 @@
       </c>
       <c r="BX7" s="5">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BY7" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3943,7 +3582,7 @@
       </c>
       <c r="BX8" s="5">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BY8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4178,7 +3817,7 @@
       </c>
       <c r="BX9" s="5">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BY9" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4413,7 +4052,7 @@
       </c>
       <c r="BX10" s="5">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BY10" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4648,7 +4287,7 @@
       </c>
       <c r="BX11" s="5">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BY11" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4883,7 +4522,7 @@
       </c>
       <c r="BX12" s="5">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BY12" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5118,7 +4757,7 @@
       </c>
       <c r="BX13" s="5">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BY13" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5353,7 +4992,7 @@
       </c>
       <c r="BX14" s="5">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BY14" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5583,18 +5222,17 @@
       <c r="BW15" t="s">
         <v>114</v>
       </c>
-      <c r="BX15" s="7">
+      <c r="BX15" s="5">
         <f>SUMPRODUCT((D15:BW15=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>17</v>
-      </c>
-      <c r="BY15" s="8" t="str">
+        <v>19</v>
+      </c>
+      <c r="BY15" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
         <v>Pablo</v>
       </c>
     </row>
     <row r="16" spans="1:77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="BX16" s="7"/>
-      <c r="BY16" s="8"/>
+      <c r="BX16" s="5"/>
     </row>
     <row r="18" spans="1:71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
@@ -5606,10 +5244,10 @@
       <c r="E18" t="s">
         <v>92</v>
       </c>
-      <c r="F18" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="G18" s="9" t="s">
+      <c r="F18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="7" t="s">
         <v>77</v>
       </c>
       <c r="J18" t="s">
@@ -5618,10 +5256,10 @@
       <c r="K18" t="s">
         <v>76</v>
       </c>
-      <c r="L18" s="9" t="s">
+      <c r="L18" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="M18" s="9" t="s">
+      <c r="M18" s="7" t="s">
         <v>95</v>
       </c>
       <c r="P18" t="s">
@@ -5639,28 +5277,34 @@
       <c r="V18" t="s">
         <v>101</v>
       </c>
-      <c r="W18" s="9" t="s">
+      <c r="W18" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="X18" s="9" t="s">
+      <c r="X18" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="Y18" s="9" t="s">
+      <c r="Y18" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="AB18" s="9" t="s">
+      <c r="AB18" s="7" t="s">
         <v>80</v>
       </c>
       <c r="AC18" t="s">
         <v>102</v>
       </c>
-      <c r="AH18" s="9" t="s">
+      <c r="AD18" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH18" s="7" t="s">
         <v>76</v>
       </c>
       <c r="AI18" t="s">
         <v>103</v>
       </c>
-      <c r="AN18" s="9" t="s">
+      <c r="AJ18" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="AN18" s="7" t="s">
         <v>76</v>
       </c>
       <c r="AO18" t="s">
@@ -5675,22 +5319,22 @@
       <c r="AZ18" t="s">
         <v>85</v>
       </c>
-      <c r="BA18" s="9" t="s">
+      <c r="BA18" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="BF18" s="9" t="s">
+      <c r="BF18" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="BG18" s="9" t="s">
+      <c r="BG18" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="BL18" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="BM18" s="9" t="s">
+      <c r="BL18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="BM18" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="BR18" s="9" t="s">
+      <c r="BR18" s="7" t="s">
         <v>90</v>
       </c>
       <c r="BS18" t="s">
@@ -5699,163 +5343,173 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D16">
-    <cfRule type="cellIs" dxfId="62" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="34" operator="equal">
       <formula>$D$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E16">
-    <cfRule type="cellIs" dxfId="61" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="33" operator="equal">
       <formula>$E$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F15">
-    <cfRule type="cellIs" dxfId="60" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="10" operator="equal">
       <formula>$F$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G15">
-    <cfRule type="cellIs" dxfId="59" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="7" operator="equal">
       <formula>$G$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J16">
-    <cfRule type="cellIs" dxfId="58" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="32" operator="equal">
       <formula>$J$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K15">
-    <cfRule type="cellIs" dxfId="57" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="30" operator="equal">
       <formula>$K$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L15">
-    <cfRule type="cellIs" dxfId="56" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="9" operator="equal">
       <formula>$L$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M15">
-    <cfRule type="cellIs" dxfId="55" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="8" operator="equal">
       <formula>$M$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P15">
-    <cfRule type="cellIs" dxfId="54" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="29" operator="equal">
       <formula>$P$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q15">
-    <cfRule type="cellIs" dxfId="53" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="28" operator="equal">
       <formula>$Q$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R15">
+    <cfRule type="cellIs" dxfId="56" priority="6" operator="equal">
+      <formula>$R$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S2:S15">
+    <cfRule type="cellIs" dxfId="55" priority="5" operator="equal">
+      <formula>$S$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="V2:V16">
-    <cfRule type="cellIs" dxfId="52" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="31" operator="equal">
       <formula>$V$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W15">
-    <cfRule type="cellIs" dxfId="51" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="27" operator="equal">
       <formula>$W$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="X2:X15">
+    <cfRule type="cellIs" dxfId="52" priority="4" operator="equal">
+      <formula>$X$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y2:Y15">
+    <cfRule type="cellIs" dxfId="51" priority="3" operator="equal">
+      <formula>$Y$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB15">
-    <cfRule type="cellIs" dxfId="50" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="26" operator="equal">
       <formula>$AB$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC15">
-    <cfRule type="cellIs" dxfId="49" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="24" operator="equal">
       <formula>$AC$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH15">
-    <cfRule type="cellIs" dxfId="48" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="25" operator="equal">
       <formula>$AH$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI15">
-    <cfRule type="cellIs" dxfId="47" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="23" operator="equal">
       <formula>$AI$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN15">
-    <cfRule type="cellIs" dxfId="46" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="20" operator="equal">
       <formula>$AN$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO2:AO15">
-    <cfRule type="cellIs" dxfId="45" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="19" operator="equal">
       <formula>$AO$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT15">
-    <cfRule type="cellIs" dxfId="44" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="22" operator="equal">
       <formula>$AT$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU15">
-    <cfRule type="cellIs" dxfId="43" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="21" operator="equal">
       <formula>$AU$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ2:AZ15">
-    <cfRule type="cellIs" dxfId="42" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="18" operator="equal">
       <formula>$AZ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA2:BA15">
-    <cfRule type="cellIs" dxfId="41" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="17" operator="equal">
       <formula>$BA$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BF2:BF15">
-    <cfRule type="cellIs" dxfId="40" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="16" operator="equal">
       <formula>$BF$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG2:BG15">
-    <cfRule type="cellIs" dxfId="39" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="15" operator="equal">
       <formula>$BG$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL2:BL15">
-    <cfRule type="cellIs" dxfId="38" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="14" operator="equal">
       <formula>$BL$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM2:BM15">
-    <cfRule type="cellIs" dxfId="37" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="11" operator="equal">
       <formula>$BM$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BR2:BR15">
-    <cfRule type="cellIs" dxfId="36" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="13" operator="equal">
       <formula>$BR$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS2:BS15">
-    <cfRule type="cellIs" dxfId="35" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="12" operator="equal">
       <formula>$BS$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R15">
-    <cfRule type="cellIs" dxfId="34" priority="4" operator="equal">
-      <formula>$R$18</formula>
+  <conditionalFormatting sqref="AD2:AD15">
+    <cfRule type="cellIs" dxfId="34" priority="2" operator="equal">
+      <formula>$AD$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S15">
-    <cfRule type="cellIs" dxfId="33" priority="3" operator="equal">
-      <formula>$S$18</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X2:X15">
-    <cfRule type="cellIs" dxfId="32" priority="2" operator="equal">
-      <formula>$X$18</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y2:Y15">
+  <conditionalFormatting sqref="AJ2:AJ15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$Y$18</formula>
+      <formula>$AJ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/predicciones.xlsx
+++ b/predicciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User710\Documents\Proyectos\Tabla-mundial-main\Tabla-mundial-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A08E08-5D55-43B3-83B1-1B6183A67D8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C72A6FBB-A03A-4686-8E26-A762E6AF9F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="145">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -593,203 +593,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="105">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="77">
     <dxf>
       <fill>
         <patternFill>
@@ -1343,10 +1147,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="104"/>
-      <tableStyleElement type="headerRow" dxfId="103"/>
-      <tableStyleElement type="firstRowStripe" dxfId="102"/>
-      <tableStyleElement type="secondRowStripe" dxfId="101"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="76"/>
+      <tableStyleElement type="headerRow" dxfId="75"/>
+      <tableStyleElement type="firstRowStripe" dxfId="74"/>
+      <tableStyleElement type="secondRowStripe" dxfId="73"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1438,10 +1242,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="100">
+    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="72">
       <calculatedColumnFormula>SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="99">
+    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="71">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2407,7 +2211,7 @@
       </c>
       <c r="BX3" s="5">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BY3" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2642,7 +2446,7 @@
       </c>
       <c r="BX4" s="5">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BY4" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2877,7 +2681,7 @@
       </c>
       <c r="BX5" s="5">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BY5" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3112,7 +2916,7 @@
       </c>
       <c r="BX6" s="5">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BY6" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3347,7 +3151,7 @@
       </c>
       <c r="BX7" s="5">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BY7" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3582,7 +3386,7 @@
       </c>
       <c r="BX8" s="5">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BY8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3817,7 +3621,7 @@
       </c>
       <c r="BX9" s="5">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BY9" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4052,7 +3856,7 @@
       </c>
       <c r="BX10" s="5">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BY10" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4522,7 +4326,7 @@
       </c>
       <c r="BX12" s="5">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BY12" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4992,7 +4796,7 @@
       </c>
       <c r="BX14" s="5">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BY14" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5224,7 +5028,7 @@
       </c>
       <c r="BX15" s="5">
         <f>SUMPRODUCT((D15:BW15=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BY15" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5295,6 +5099,9 @@
       <c r="AD18" t="s">
         <v>80</v>
       </c>
+      <c r="AE18" t="s">
+        <v>76</v>
+      </c>
       <c r="AH18" s="7" t="s">
         <v>76</v>
       </c>
@@ -5303,6 +5110,9 @@
       </c>
       <c r="AJ18" s="7" t="s">
         <v>82</v>
+      </c>
+      <c r="AK18" s="7" t="s">
+        <v>104</v>
       </c>
       <c r="AN18" s="7" t="s">
         <v>76</v>
@@ -5343,173 +5153,183 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D16">
-    <cfRule type="cellIs" dxfId="66" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="36" operator="equal">
       <formula>$D$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E16">
-    <cfRule type="cellIs" dxfId="65" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="35" operator="equal">
       <formula>$E$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F15">
-    <cfRule type="cellIs" dxfId="64" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="12" operator="equal">
       <formula>$F$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G15">
-    <cfRule type="cellIs" dxfId="63" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="9" operator="equal">
       <formula>$G$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J16">
-    <cfRule type="cellIs" dxfId="62" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="34" operator="equal">
       <formula>$J$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K15">
-    <cfRule type="cellIs" dxfId="61" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="32" operator="equal">
       <formula>$K$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L15">
-    <cfRule type="cellIs" dxfId="60" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="11" operator="equal">
       <formula>$L$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M15">
-    <cfRule type="cellIs" dxfId="59" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="10" operator="equal">
       <formula>$M$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P15">
-    <cfRule type="cellIs" dxfId="58" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="31" operator="equal">
       <formula>$P$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q15">
-    <cfRule type="cellIs" dxfId="57" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="30" operator="equal">
       <formula>$Q$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R15">
-    <cfRule type="cellIs" dxfId="56" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="8" operator="equal">
       <formula>$R$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S15">
-    <cfRule type="cellIs" dxfId="55" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="7" operator="equal">
       <formula>$S$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V16">
-    <cfRule type="cellIs" dxfId="54" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="33" operator="equal">
       <formula>$V$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W15">
-    <cfRule type="cellIs" dxfId="53" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="29" operator="equal">
       <formula>$W$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X15">
-    <cfRule type="cellIs" dxfId="52" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="6" operator="equal">
       <formula>$X$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y15">
-    <cfRule type="cellIs" dxfId="51" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="5" operator="equal">
       <formula>$Y$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB15">
-    <cfRule type="cellIs" dxfId="50" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="28" operator="equal">
       <formula>$AB$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC15">
-    <cfRule type="cellIs" dxfId="49" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="26" operator="equal">
       <formula>$AC$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AD2:AD15">
+    <cfRule type="cellIs" dxfId="52" priority="4" operator="equal">
+      <formula>$AD$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE2:AE15">
+    <cfRule type="cellIs" dxfId="51" priority="2" operator="equal">
+      <formula>$AE$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH15">
-    <cfRule type="cellIs" dxfId="48" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="27" operator="equal">
       <formula>$AH$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI15">
-    <cfRule type="cellIs" dxfId="47" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="25" operator="equal">
       <formula>$AI$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AJ2:AJ15">
+    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
+      <formula>$AJ$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN15">
-    <cfRule type="cellIs" dxfId="46" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="22" operator="equal">
       <formula>$AN$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO2:AO15">
-    <cfRule type="cellIs" dxfId="45" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="21" operator="equal">
       <formula>$AO$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT15">
-    <cfRule type="cellIs" dxfId="44" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="24" operator="equal">
       <formula>$AT$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU15">
-    <cfRule type="cellIs" dxfId="43" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="23" operator="equal">
       <formula>$AU$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ2:AZ15">
-    <cfRule type="cellIs" dxfId="42" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="20" operator="equal">
       <formula>$AZ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA2:BA15">
-    <cfRule type="cellIs" dxfId="41" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="19" operator="equal">
       <formula>$BA$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BF2:BF15">
-    <cfRule type="cellIs" dxfId="40" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="18" operator="equal">
       <formula>$BF$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG2:BG15">
-    <cfRule type="cellIs" dxfId="39" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="17" operator="equal">
       <formula>$BG$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL2:BL15">
-    <cfRule type="cellIs" dxfId="38" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="16" operator="equal">
       <formula>$BL$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM2:BM15">
-    <cfRule type="cellIs" dxfId="37" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="13" operator="equal">
       <formula>$BM$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BR2:BR15">
-    <cfRule type="cellIs" dxfId="36" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="15" operator="equal">
       <formula>$BR$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS2:BS15">
-    <cfRule type="cellIs" dxfId="35" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="14" operator="equal">
       <formula>$BS$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD2:AD15">
-    <cfRule type="cellIs" dxfId="34" priority="2" operator="equal">
-      <formula>$AD$18</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ2:AJ15">
+  <conditionalFormatting sqref="AK2:AK15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$AJ$18</formula>
+      <formula>$AK$18</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/predicciones.xlsx
+++ b/predicciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User710\Documents\Proyectos\Tabla-mundial-main\Tabla-mundial-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C72A6FBB-A03A-4686-8E26-A762E6AF9F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B5D795-72B5-4FD7-8AB4-A0E1074D3358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="145">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -593,7 +593,21 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="77">
+  <dxfs count="79">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1147,10 +1161,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="76"/>
-      <tableStyleElement type="headerRow" dxfId="75"/>
-      <tableStyleElement type="firstRowStripe" dxfId="74"/>
-      <tableStyleElement type="secondRowStripe" dxfId="73"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="78"/>
+      <tableStyleElement type="headerRow" dxfId="77"/>
+      <tableStyleElement type="firstRowStripe" dxfId="76"/>
+      <tableStyleElement type="secondRowStripe" dxfId="75"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1242,10 +1256,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="72">
+    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="74">
       <calculatedColumnFormula>SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="71">
+    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="73">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2446,7 +2460,7 @@
       </c>
       <c r="BX4" s="5">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BY4" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2681,7 +2695,7 @@
       </c>
       <c r="BX5" s="5">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BY5" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2916,7 +2930,7 @@
       </c>
       <c r="BX6" s="5">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BY6" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3151,7 +3165,7 @@
       </c>
       <c r="BX7" s="5">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BY7" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3386,7 +3400,7 @@
       </c>
       <c r="BX8" s="5">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BY8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3621,7 +3635,7 @@
       </c>
       <c r="BX9" s="5">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BY9" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3856,7 +3870,7 @@
       </c>
       <c r="BX10" s="5">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BY10" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4091,7 +4105,7 @@
       </c>
       <c r="BX11" s="5">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BY11" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4326,7 +4340,7 @@
       </c>
       <c r="BX12" s="5">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BY12" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4561,7 +4575,7 @@
       </c>
       <c r="BX13" s="5">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BY13" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4796,7 +4810,7 @@
       </c>
       <c r="BX14" s="5">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BY14" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5028,7 +5042,7 @@
       </c>
       <c r="BX15" s="5">
         <f>SUMPRODUCT((D15:BW15=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BY15" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5126,6 +5140,9 @@
       <c r="AU18" t="s">
         <v>76</v>
       </c>
+      <c r="AV18" t="s">
+        <v>107</v>
+      </c>
       <c r="AZ18" t="s">
         <v>85</v>
       </c>
@@ -5153,183 +5170,188 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D16">
-    <cfRule type="cellIs" dxfId="70" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="37" operator="equal">
       <formula>$D$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E16">
-    <cfRule type="cellIs" dxfId="69" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="36" operator="equal">
       <formula>$E$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F15">
-    <cfRule type="cellIs" dxfId="68" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="13" operator="equal">
       <formula>$F$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G15">
-    <cfRule type="cellIs" dxfId="67" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="10" operator="equal">
       <formula>$G$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J16">
-    <cfRule type="cellIs" dxfId="66" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="35" operator="equal">
       <formula>$J$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K15">
-    <cfRule type="cellIs" dxfId="65" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="33" operator="equal">
       <formula>$K$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L15">
-    <cfRule type="cellIs" dxfId="64" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="12" operator="equal">
       <formula>$L$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M15">
-    <cfRule type="cellIs" dxfId="63" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="11" operator="equal">
       <formula>$M$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P15">
-    <cfRule type="cellIs" dxfId="62" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="32" operator="equal">
       <formula>$P$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q15">
-    <cfRule type="cellIs" dxfId="61" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="31" operator="equal">
       <formula>$Q$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R15">
-    <cfRule type="cellIs" dxfId="60" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="9" operator="equal">
       <formula>$R$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S15">
-    <cfRule type="cellIs" dxfId="59" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="8" operator="equal">
       <formula>$S$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V16">
-    <cfRule type="cellIs" dxfId="58" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="34" operator="equal">
       <formula>$V$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W15">
-    <cfRule type="cellIs" dxfId="57" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="30" operator="equal">
       <formula>$W$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X15">
-    <cfRule type="cellIs" dxfId="56" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="7" operator="equal">
       <formula>$X$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y15">
-    <cfRule type="cellIs" dxfId="55" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="6" operator="equal">
       <formula>$Y$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB15">
-    <cfRule type="cellIs" dxfId="54" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="29" operator="equal">
       <formula>$AB$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC15">
-    <cfRule type="cellIs" dxfId="53" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="27" operator="equal">
       <formula>$AC$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD15">
-    <cfRule type="cellIs" dxfId="52" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="5" operator="equal">
       <formula>$AD$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE15">
-    <cfRule type="cellIs" dxfId="51" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="3" operator="equal">
       <formula>$AE$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH15">
-    <cfRule type="cellIs" dxfId="50" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="28" operator="equal">
       <formula>$AH$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI15">
-    <cfRule type="cellIs" dxfId="49" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="26" operator="equal">
       <formula>$AI$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ2:AJ15">
-    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="4" operator="equal">
       <formula>$AJ$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AK2:AK15">
+    <cfRule type="cellIs" dxfId="49" priority="2" operator="equal">
+      <formula>$AK$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN15">
-    <cfRule type="cellIs" dxfId="47" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="23" operator="equal">
       <formula>$AN$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO2:AO15">
-    <cfRule type="cellIs" dxfId="46" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="22" operator="equal">
       <formula>$AO$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT15">
-    <cfRule type="cellIs" dxfId="45" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="25" operator="equal">
       <formula>$AT$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU15">
-    <cfRule type="cellIs" dxfId="44" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="24" operator="equal">
       <formula>$AU$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ2:AZ15">
-    <cfRule type="cellIs" dxfId="43" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="21" operator="equal">
       <formula>$AZ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA2:BA15">
-    <cfRule type="cellIs" dxfId="42" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="20" operator="equal">
       <formula>$BA$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BF2:BF15">
-    <cfRule type="cellIs" dxfId="41" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="19" operator="equal">
       <formula>$BF$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG2:BG15">
-    <cfRule type="cellIs" dxfId="40" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="18" operator="equal">
       <formula>$BG$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL2:BL15">
-    <cfRule type="cellIs" dxfId="39" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="17" operator="equal">
       <formula>$BL$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM2:BM15">
-    <cfRule type="cellIs" dxfId="38" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="14" operator="equal">
       <formula>$BM$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BR2:BR15">
-    <cfRule type="cellIs" dxfId="37" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="16" operator="equal">
       <formula>$BR$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS2:BS15">
-    <cfRule type="cellIs" dxfId="36" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="15" operator="equal">
       <formula>$BS$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK2:AK15">
+  <conditionalFormatting sqref="AV2:AV15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$AK$18</formula>
+      <formula>$AV$18</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/predicciones.xlsx
+++ b/predicciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User710\Documents\Proyectos\Tabla-mundial-main\Tabla-mundial-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B5D795-72B5-4FD7-8AB4-A0E1074D3358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{592CA434-E9CA-4A54-8D7B-8DAB6894DDB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="144">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -501,9 +501,6 @@
   </si>
   <si>
     <t xml:space="preserve">Ernesto </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -593,7 +590,294 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="79">
+  <dxfs count="120">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1161,10 +1445,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="78"/>
-      <tableStyleElement type="headerRow" dxfId="77"/>
-      <tableStyleElement type="firstRowStripe" dxfId="76"/>
-      <tableStyleElement type="secondRowStripe" dxfId="75"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="119"/>
+      <tableStyleElement type="headerRow" dxfId="118"/>
+      <tableStyleElement type="firstRowStripe" dxfId="117"/>
+      <tableStyleElement type="secondRowStripe" dxfId="116"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1256,10 +1540,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="74">
+    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="115">
       <calculatedColumnFormula>SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="73">
+    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="114">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1884,7 +2168,7 @@
         <v>76</v>
       </c>
       <c r="AO2" s="3" t="s">
-        <v>144</v>
+        <v>76</v>
       </c>
       <c r="AP2" s="3" t="s">
         <v>83</v>
@@ -1990,7 +2274,7 @@
       </c>
       <c r="BX2" s="5">
         <f t="shared" ref="BX2:BX14" si="0">SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BY2" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2695,7 +2979,7 @@
       </c>
       <c r="BX5" s="5">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BY5" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4810,7 +5094,7 @@
       </c>
       <c r="BX14" s="5">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BY14" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5131,7 +5415,10 @@
       <c r="AN18" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="AO18" t="s">
+      <c r="AO18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="AP18" s="7" t="s">
         <v>76</v>
       </c>
       <c r="AT18" t="s">
@@ -5142,6 +5429,9 @@
       </c>
       <c r="AV18" t="s">
         <v>107</v>
+      </c>
+      <c r="AW18" t="s">
+        <v>76</v>
       </c>
       <c r="AZ18" t="s">
         <v>85</v>
@@ -5170,188 +5460,198 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D16">
-    <cfRule type="cellIs" dxfId="72" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="39" operator="equal">
       <formula>$D$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E16">
-    <cfRule type="cellIs" dxfId="71" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="38" operator="equal">
       <formula>$E$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F15">
-    <cfRule type="cellIs" dxfId="70" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="15" operator="equal">
       <formula>$F$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G15">
-    <cfRule type="cellIs" dxfId="69" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="12" operator="equal">
       <formula>$G$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J16">
-    <cfRule type="cellIs" dxfId="68" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="37" operator="equal">
       <formula>$J$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K15">
-    <cfRule type="cellIs" dxfId="67" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="35" operator="equal">
       <formula>$K$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L15">
-    <cfRule type="cellIs" dxfId="66" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="14" operator="equal">
       <formula>$L$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M15">
-    <cfRule type="cellIs" dxfId="65" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="13" operator="equal">
       <formula>$M$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P15">
-    <cfRule type="cellIs" dxfId="64" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="34" operator="equal">
       <formula>$P$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q15">
-    <cfRule type="cellIs" dxfId="63" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="33" operator="equal">
       <formula>$Q$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R15">
-    <cfRule type="cellIs" dxfId="62" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="11" operator="equal">
       <formula>$R$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S15">
-    <cfRule type="cellIs" dxfId="61" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="10" operator="equal">
       <formula>$S$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V16">
-    <cfRule type="cellIs" dxfId="60" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="36" operator="equal">
       <formula>$V$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W15">
-    <cfRule type="cellIs" dxfId="59" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="32" operator="equal">
       <formula>$W$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X15">
-    <cfRule type="cellIs" dxfId="58" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="9" operator="equal">
       <formula>$X$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y15">
-    <cfRule type="cellIs" dxfId="57" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="8" operator="equal">
       <formula>$Y$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB15">
-    <cfRule type="cellIs" dxfId="56" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="31" operator="equal">
       <formula>$AB$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC15">
-    <cfRule type="cellIs" dxfId="55" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="29" operator="equal">
       <formula>$AC$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD15">
-    <cfRule type="cellIs" dxfId="54" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="7" operator="equal">
       <formula>$AD$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE15">
-    <cfRule type="cellIs" dxfId="53" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="5" operator="equal">
       <formula>$AE$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH15">
-    <cfRule type="cellIs" dxfId="52" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="30" operator="equal">
       <formula>$AH$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI15">
-    <cfRule type="cellIs" dxfId="51" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="28" operator="equal">
       <formula>$AI$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ2:AJ15">
-    <cfRule type="cellIs" dxfId="50" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="6" operator="equal">
       <formula>$AJ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK2:AK15">
-    <cfRule type="cellIs" dxfId="49" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="4" operator="equal">
       <formula>$AK$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN15">
-    <cfRule type="cellIs" dxfId="48" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="25" operator="equal">
       <formula>$AN$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO2:AO15">
-    <cfRule type="cellIs" dxfId="47" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="24" operator="equal">
       <formula>$AO$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT15">
-    <cfRule type="cellIs" dxfId="46" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="27" operator="equal">
       <formula>$AT$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU15">
-    <cfRule type="cellIs" dxfId="45" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="26" operator="equal">
       <formula>$AU$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AV2:AV15">
+    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
+      <formula>$AV$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AZ2:AZ15">
-    <cfRule type="cellIs" dxfId="44" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="23" operator="equal">
       <formula>$AZ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA2:BA15">
-    <cfRule type="cellIs" dxfId="43" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="22" operator="equal">
       <formula>$BA$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BF2:BF15">
-    <cfRule type="cellIs" dxfId="42" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="21" operator="equal">
       <formula>$BF$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG2:BG15">
-    <cfRule type="cellIs" dxfId="41" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="20" operator="equal">
       <formula>$BG$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL2:BL15">
-    <cfRule type="cellIs" dxfId="40" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="19" operator="equal">
       <formula>$BL$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM2:BM15">
-    <cfRule type="cellIs" dxfId="39" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="16" operator="equal">
       <formula>$BM$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BR2:BR15">
-    <cfRule type="cellIs" dxfId="38" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="18" operator="equal">
       <formula>$BR$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS2:BS15">
-    <cfRule type="cellIs" dxfId="37" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="17" operator="equal">
       <formula>$BS$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AV2:AV15">
+  <conditionalFormatting sqref="AW2:AW15">
+    <cfRule type="cellIs" dxfId="39" priority="2" operator="equal">
+      <formula>$AW$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AP2:AP15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$AV$18</formula>
+      <formula>$AP$18</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/predicciones.xlsx
+++ b/predicciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User710\Documents\Proyectos\Tabla-mundial-main\Tabla-mundial-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{592CA434-E9CA-4A54-8D7B-8DAB6894DDB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3437226-7A10-49C5-AC47-4DF89678EF94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="144">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -590,252 +590,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="120">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="85">
     <dxf>
       <fill>
         <patternFill>
@@ -1445,10 +1200,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="119"/>
-      <tableStyleElement type="headerRow" dxfId="118"/>
-      <tableStyleElement type="firstRowStripe" dxfId="117"/>
-      <tableStyleElement type="secondRowStripe" dxfId="116"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="84"/>
+      <tableStyleElement type="headerRow" dxfId="83"/>
+      <tableStyleElement type="firstRowStripe" dxfId="82"/>
+      <tableStyleElement type="secondRowStripe" dxfId="81"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1540,10 +1295,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="115">
+    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="80">
       <calculatedColumnFormula>SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="114">
+    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="79">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2509,7 +2264,7 @@
       </c>
       <c r="BX3" s="5">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BY3" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2979,7 +2734,7 @@
       </c>
       <c r="BX5" s="5">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BY5" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3214,7 +2969,7 @@
       </c>
       <c r="BX6" s="5">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BY6" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3684,7 +3439,7 @@
       </c>
       <c r="BX8" s="5">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BY8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3919,7 +3674,7 @@
       </c>
       <c r="BX9" s="5">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BY9" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4154,7 +3909,7 @@
       </c>
       <c r="BX10" s="5">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BY10" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4389,7 +4144,7 @@
       </c>
       <c r="BX11" s="5">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BY11" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4624,7 +4379,7 @@
       </c>
       <c r="BX12" s="5">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BY12" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5094,7 +4849,7 @@
       </c>
       <c r="BX14" s="5">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BY14" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5326,7 +5081,7 @@
       </c>
       <c r="BX15" s="5">
         <f>SUMPRODUCT((D15:BW15=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BY15" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5421,6 +5176,9 @@
       <c r="AP18" s="7" t="s">
         <v>76</v>
       </c>
+      <c r="AQ18" s="7" t="s">
+        <v>106</v>
+      </c>
       <c r="AT18" t="s">
         <v>76</v>
       </c>
@@ -5460,198 +5218,203 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D16">
-    <cfRule type="cellIs" dxfId="76" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="40" operator="equal">
       <formula>$D$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E16">
-    <cfRule type="cellIs" dxfId="75" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="39" operator="equal">
       <formula>$E$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F15">
-    <cfRule type="cellIs" dxfId="74" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="16" operator="equal">
       <formula>$F$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G15">
-    <cfRule type="cellIs" dxfId="73" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="13" operator="equal">
       <formula>$G$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J16">
-    <cfRule type="cellIs" dxfId="72" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="38" operator="equal">
       <formula>$J$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K15">
-    <cfRule type="cellIs" dxfId="71" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="36" operator="equal">
       <formula>$K$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L15">
-    <cfRule type="cellIs" dxfId="70" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="15" operator="equal">
       <formula>$L$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M15">
-    <cfRule type="cellIs" dxfId="69" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="14" operator="equal">
       <formula>$M$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P15">
-    <cfRule type="cellIs" dxfId="68" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="35" operator="equal">
       <formula>$P$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q15">
-    <cfRule type="cellIs" dxfId="67" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="34" operator="equal">
       <formula>$Q$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R15">
-    <cfRule type="cellIs" dxfId="66" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="12" operator="equal">
       <formula>$R$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S15">
-    <cfRule type="cellIs" dxfId="65" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="11" operator="equal">
       <formula>$S$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V16">
-    <cfRule type="cellIs" dxfId="64" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="37" operator="equal">
       <formula>$V$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W15">
-    <cfRule type="cellIs" dxfId="63" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="33" operator="equal">
       <formula>$W$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X15">
-    <cfRule type="cellIs" dxfId="62" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="10" operator="equal">
       <formula>$X$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y15">
-    <cfRule type="cellIs" dxfId="61" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="9" operator="equal">
       <formula>$Y$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB15">
-    <cfRule type="cellIs" dxfId="60" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="32" operator="equal">
       <formula>$AB$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC15">
-    <cfRule type="cellIs" dxfId="59" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="30" operator="equal">
       <formula>$AC$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD15">
-    <cfRule type="cellIs" dxfId="58" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="8" operator="equal">
       <formula>$AD$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE15">
-    <cfRule type="cellIs" dxfId="57" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="6" operator="equal">
       <formula>$AE$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH15">
-    <cfRule type="cellIs" dxfId="56" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="31" operator="equal">
       <formula>$AH$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI15">
-    <cfRule type="cellIs" dxfId="55" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="29" operator="equal">
       <formula>$AI$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ2:AJ15">
-    <cfRule type="cellIs" dxfId="54" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="7" operator="equal">
       <formula>$AJ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK2:AK15">
-    <cfRule type="cellIs" dxfId="53" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="5" operator="equal">
       <formula>$AK$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN15">
-    <cfRule type="cellIs" dxfId="52" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="26" operator="equal">
       <formula>$AN$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO2:AO15">
-    <cfRule type="cellIs" dxfId="51" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="25" operator="equal">
       <formula>$AO$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AP2:AP15">
+    <cfRule type="cellIs" dxfId="52" priority="2" operator="equal">
+      <formula>$AP$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT15">
-    <cfRule type="cellIs" dxfId="50" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="28" operator="equal">
       <formula>$AT$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU15">
-    <cfRule type="cellIs" dxfId="49" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="27" operator="equal">
       <formula>$AU$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV2:AV15">
-    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="4" operator="equal">
       <formula>$AV$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AW2:AW15">
+    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
+      <formula>$AW$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AZ2:AZ15">
-    <cfRule type="cellIs" dxfId="47" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="24" operator="equal">
       <formula>$AZ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA2:BA15">
-    <cfRule type="cellIs" dxfId="46" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="23" operator="equal">
       <formula>$BA$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BF2:BF15">
-    <cfRule type="cellIs" dxfId="45" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="22" operator="equal">
       <formula>$BF$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG2:BG15">
-    <cfRule type="cellIs" dxfId="44" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="21" operator="equal">
       <formula>$BG$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL2:BL15">
-    <cfRule type="cellIs" dxfId="43" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="20" operator="equal">
       <formula>$BL$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM2:BM15">
-    <cfRule type="cellIs" dxfId="42" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="17" operator="equal">
       <formula>$BM$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BR2:BR15">
-    <cfRule type="cellIs" dxfId="41" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="19" operator="equal">
       <formula>$BR$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS2:BS15">
-    <cfRule type="cellIs" dxfId="40" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="18" operator="equal">
       <formula>$BS$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AW2:AW15">
-    <cfRule type="cellIs" dxfId="39" priority="2" operator="equal">
-      <formula>$AW$18</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AP2:AP15">
+  <conditionalFormatting sqref="AQ2:AQ15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$AP$18</formula>
+      <formula>$AQ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/predicciones.xlsx
+++ b/predicciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User710\Documents\Proyectos\Tabla-mundial-main\Tabla-mundial-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3437226-7A10-49C5-AC47-4DF89678EF94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC4E6301-63C7-440E-BDB2-D18B11C72866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="144">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -590,7 +590,315 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="85">
+  <dxfs count="129">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1200,10 +1508,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="84"/>
-      <tableStyleElement type="headerRow" dxfId="83"/>
-      <tableStyleElement type="firstRowStripe" dxfId="82"/>
-      <tableStyleElement type="secondRowStripe" dxfId="81"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="128"/>
+      <tableStyleElement type="headerRow" dxfId="127"/>
+      <tableStyleElement type="firstRowStripe" dxfId="126"/>
+      <tableStyleElement type="secondRowStripe" dxfId="125"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1295,10 +1603,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="80">
+    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="124">
       <calculatedColumnFormula>SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="79">
+    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="123">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2029,7 +2337,7 @@
       </c>
       <c r="BX2" s="5">
         <f t="shared" ref="BX2:BX14" si="0">SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BY2" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2264,7 +2572,7 @@
       </c>
       <c r="BX3" s="5">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BY3" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2499,7 +2807,7 @@
       </c>
       <c r="BX4" s="5">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BY4" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2734,7 +3042,7 @@
       </c>
       <c r="BX5" s="5">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BY5" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2969,7 +3277,7 @@
       </c>
       <c r="BX6" s="5">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BY6" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3204,7 +3512,7 @@
       </c>
       <c r="BX7" s="5">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BY7" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3439,7 +3747,7 @@
       </c>
       <c r="BX8" s="5">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BY8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3674,7 +3982,7 @@
       </c>
       <c r="BX9" s="5">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BY9" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3909,7 +4217,7 @@
       </c>
       <c r="BX10" s="5">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BY10" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4144,7 +4452,7 @@
       </c>
       <c r="BX11" s="5">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BY11" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4379,7 +4687,7 @@
       </c>
       <c r="BX12" s="5">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BY12" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4614,7 +4922,7 @@
       </c>
       <c r="BX13" s="5">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BY13" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4849,7 +5157,7 @@
       </c>
       <c r="BX14" s="5">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BY14" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5081,7 +5389,7 @@
       </c>
       <c r="BX15" s="5">
         <f>SUMPRODUCT((D15:BW15=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BY15" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5197,11 +5505,17 @@
       <c r="BA18" s="7" t="s">
         <v>109</v>
       </c>
+      <c r="BB18" s="7" t="s">
+        <v>85</v>
+      </c>
       <c r="BF18" s="7" t="s">
         <v>87</v>
       </c>
       <c r="BG18" s="7" t="s">
         <v>110</v>
+      </c>
+      <c r="BH18" t="s">
+        <v>87</v>
       </c>
       <c r="BL18" s="7" t="s">
         <v>76</v>
@@ -5218,203 +5532,213 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D16">
-    <cfRule type="cellIs" dxfId="78" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="42" operator="equal">
       <formula>$D$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E16">
-    <cfRule type="cellIs" dxfId="77" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="41" operator="equal">
       <formula>$E$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F15">
-    <cfRule type="cellIs" dxfId="76" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="18" operator="equal">
       <formula>$F$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G15">
-    <cfRule type="cellIs" dxfId="75" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="15" operator="equal">
       <formula>$G$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J16">
-    <cfRule type="cellIs" dxfId="74" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="40" operator="equal">
       <formula>$J$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K15">
-    <cfRule type="cellIs" dxfId="73" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="38" operator="equal">
       <formula>$K$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L15">
-    <cfRule type="cellIs" dxfId="72" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="17" operator="equal">
       <formula>$L$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M15">
-    <cfRule type="cellIs" dxfId="71" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="16" operator="equal">
       <formula>$M$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P15">
-    <cfRule type="cellIs" dxfId="70" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="37" operator="equal">
       <formula>$P$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q15">
-    <cfRule type="cellIs" dxfId="69" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="36" operator="equal">
       <formula>$Q$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R15">
-    <cfRule type="cellIs" dxfId="68" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="14" operator="equal">
       <formula>$R$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S15">
-    <cfRule type="cellIs" dxfId="67" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="13" operator="equal">
       <formula>$S$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V16">
-    <cfRule type="cellIs" dxfId="66" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="39" operator="equal">
       <formula>$V$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W15">
-    <cfRule type="cellIs" dxfId="65" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="35" operator="equal">
       <formula>$W$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X15">
-    <cfRule type="cellIs" dxfId="64" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="12" operator="equal">
       <formula>$X$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y15">
-    <cfRule type="cellIs" dxfId="63" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="11" operator="equal">
       <formula>$Y$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB15">
-    <cfRule type="cellIs" dxfId="62" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="34" operator="equal">
       <formula>$AB$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC15">
-    <cfRule type="cellIs" dxfId="61" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="32" operator="equal">
       <formula>$AC$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD15">
-    <cfRule type="cellIs" dxfId="60" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="10" operator="equal">
       <formula>$AD$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE15">
-    <cfRule type="cellIs" dxfId="59" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="8" operator="equal">
       <formula>$AE$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH15">
-    <cfRule type="cellIs" dxfId="58" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="33" operator="equal">
       <formula>$AH$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI15">
-    <cfRule type="cellIs" dxfId="57" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="31" operator="equal">
       <formula>$AI$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ2:AJ15">
-    <cfRule type="cellIs" dxfId="56" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="9" operator="equal">
       <formula>$AJ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK2:AK15">
-    <cfRule type="cellIs" dxfId="55" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="7" operator="equal">
       <formula>$AK$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN15">
-    <cfRule type="cellIs" dxfId="54" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="28" operator="equal">
       <formula>$AN$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO2:AO15">
-    <cfRule type="cellIs" dxfId="53" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="27" operator="equal">
       <formula>$AO$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP2:AP15">
-    <cfRule type="cellIs" dxfId="52" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="4" operator="equal">
       <formula>$AP$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AQ2:AQ15">
+    <cfRule type="cellIs" dxfId="55" priority="3" operator="equal">
+      <formula>$AQ$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT15">
-    <cfRule type="cellIs" dxfId="51" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="30" operator="equal">
       <formula>$AT$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU15">
-    <cfRule type="cellIs" dxfId="50" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="29" operator="equal">
       <formula>$AU$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV2:AV15">
-    <cfRule type="cellIs" dxfId="49" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="6" operator="equal">
       <formula>$AV$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW2:AW15">
-    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="5" operator="equal">
       <formula>$AW$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ2:AZ15">
-    <cfRule type="cellIs" dxfId="47" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="26" operator="equal">
       <formula>$AZ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA2:BA15">
-    <cfRule type="cellIs" dxfId="46" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="25" operator="equal">
       <formula>$BA$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BF2:BF15">
-    <cfRule type="cellIs" dxfId="45" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="24" operator="equal">
       <formula>$BF$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG2:BG15">
-    <cfRule type="cellIs" dxfId="44" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="23" operator="equal">
       <formula>$BG$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL2:BL15">
-    <cfRule type="cellIs" dxfId="43" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="22" operator="equal">
       <formula>$BL$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM2:BM15">
-    <cfRule type="cellIs" dxfId="42" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="19" operator="equal">
       <formula>$BM$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BR2:BR15">
-    <cfRule type="cellIs" dxfId="41" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="21" operator="equal">
       <formula>$BR$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS2:BS15">
-    <cfRule type="cellIs" dxfId="40" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="20" operator="equal">
       <formula>$BS$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AQ2:AQ15">
+  <conditionalFormatting sqref="BH2:BH15">
+    <cfRule type="cellIs" dxfId="42" priority="2" operator="equal">
+      <formula>$BH$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BB2:BB15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$AQ$18</formula>
+      <formula>$BB$18</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/predicciones.xlsx
+++ b/predicciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User710\Documents\Proyectos\Tabla-mundial-main\Tabla-mundial-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC4E6301-63C7-440E-BDB2-D18B11C72866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB506DF-1D10-444E-A756-D4AB176FE464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="144">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -590,273 +590,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="129">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="91">
     <dxf>
       <fill>
         <patternFill>
@@ -1508,10 +1242,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="128"/>
-      <tableStyleElement type="headerRow" dxfId="127"/>
-      <tableStyleElement type="firstRowStripe" dxfId="126"/>
-      <tableStyleElement type="secondRowStripe" dxfId="125"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="90"/>
+      <tableStyleElement type="headerRow" dxfId="89"/>
+      <tableStyleElement type="firstRowStripe" dxfId="88"/>
+      <tableStyleElement type="secondRowStripe" dxfId="87"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1603,10 +1337,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="124">
+    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="86">
       <calculatedColumnFormula>SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="123">
+    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="85">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3042,7 +2776,7 @@
       </c>
       <c r="BX5" s="5">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BY5" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4217,7 +3951,7 @@
       </c>
       <c r="BX10" s="5">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BY10" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5508,6 +5242,9 @@
       <c r="BB18" s="7" t="s">
         <v>85</v>
       </c>
+      <c r="BC18" s="7" t="s">
+        <v>109</v>
+      </c>
       <c r="BF18" s="7" t="s">
         <v>87</v>
       </c>
@@ -5532,213 +5269,218 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D16">
-    <cfRule type="cellIs" dxfId="82" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="43" operator="equal">
       <formula>$D$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E16">
-    <cfRule type="cellIs" dxfId="81" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="42" operator="equal">
       <formula>$E$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F15">
-    <cfRule type="cellIs" dxfId="80" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="19" operator="equal">
       <formula>$F$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G15">
-    <cfRule type="cellIs" dxfId="79" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="16" operator="equal">
       <formula>$G$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J16">
-    <cfRule type="cellIs" dxfId="78" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="41" operator="equal">
       <formula>$J$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K15">
-    <cfRule type="cellIs" dxfId="77" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="39" operator="equal">
       <formula>$K$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L15">
-    <cfRule type="cellIs" dxfId="76" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="18" operator="equal">
       <formula>$L$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M15">
-    <cfRule type="cellIs" dxfId="75" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="17" operator="equal">
       <formula>$M$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P15">
-    <cfRule type="cellIs" dxfId="74" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="38" operator="equal">
       <formula>$P$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q15">
-    <cfRule type="cellIs" dxfId="73" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="37" operator="equal">
       <formula>$Q$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R15">
-    <cfRule type="cellIs" dxfId="72" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="15" operator="equal">
       <formula>$R$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S15">
-    <cfRule type="cellIs" dxfId="71" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="14" operator="equal">
       <formula>$S$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V16">
-    <cfRule type="cellIs" dxfId="70" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="40" operator="equal">
       <formula>$V$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W15">
-    <cfRule type="cellIs" dxfId="69" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="36" operator="equal">
       <formula>$W$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X15">
-    <cfRule type="cellIs" dxfId="68" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="13" operator="equal">
       <formula>$X$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y15">
-    <cfRule type="cellIs" dxfId="67" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="12" operator="equal">
       <formula>$Y$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB15">
-    <cfRule type="cellIs" dxfId="66" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="35" operator="equal">
       <formula>$AB$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC15">
-    <cfRule type="cellIs" dxfId="65" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="33" operator="equal">
       <formula>$AC$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD15">
-    <cfRule type="cellIs" dxfId="64" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="11" operator="equal">
       <formula>$AD$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE15">
-    <cfRule type="cellIs" dxfId="63" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="9" operator="equal">
       <formula>$AE$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH15">
-    <cfRule type="cellIs" dxfId="62" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="34" operator="equal">
       <formula>$AH$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI15">
-    <cfRule type="cellIs" dxfId="61" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="32" operator="equal">
       <formula>$AI$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ2:AJ15">
-    <cfRule type="cellIs" dxfId="60" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="10" operator="equal">
       <formula>$AJ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK2:AK15">
-    <cfRule type="cellIs" dxfId="59" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="8" operator="equal">
       <formula>$AK$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN15">
-    <cfRule type="cellIs" dxfId="58" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="29" operator="equal">
       <formula>$AN$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO2:AO15">
-    <cfRule type="cellIs" dxfId="57" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="28" operator="equal">
       <formula>$AO$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP2:AP15">
-    <cfRule type="cellIs" dxfId="56" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="5" operator="equal">
       <formula>$AP$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ2:AQ15">
-    <cfRule type="cellIs" dxfId="55" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="4" operator="equal">
       <formula>$AQ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT15">
-    <cfRule type="cellIs" dxfId="54" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="31" operator="equal">
       <formula>$AT$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU15">
-    <cfRule type="cellIs" dxfId="53" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="30" operator="equal">
       <formula>$AU$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV2:AV15">
-    <cfRule type="cellIs" dxfId="52" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="7" operator="equal">
       <formula>$AV$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW2:AW15">
-    <cfRule type="cellIs" dxfId="51" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="6" operator="equal">
       <formula>$AW$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ2:AZ15">
-    <cfRule type="cellIs" dxfId="50" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="27" operator="equal">
       <formula>$AZ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA2:BA15">
-    <cfRule type="cellIs" dxfId="49" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="26" operator="equal">
       <formula>$BA$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="BB2:BB15">
+    <cfRule type="cellIs" dxfId="50" priority="2" operator="equal">
+      <formula>$BB$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="BF2:BF15">
-    <cfRule type="cellIs" dxfId="48" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="25" operator="equal">
       <formula>$BF$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG2:BG15">
-    <cfRule type="cellIs" dxfId="47" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="24" operator="equal">
       <formula>$BG$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="BH2:BH15">
+    <cfRule type="cellIs" dxfId="47" priority="3" operator="equal">
+      <formula>$BH$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="BL2:BL15">
-    <cfRule type="cellIs" dxfId="46" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="23" operator="equal">
       <formula>$BL$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM2:BM15">
-    <cfRule type="cellIs" dxfId="45" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="20" operator="equal">
       <formula>$BM$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BR2:BR15">
-    <cfRule type="cellIs" dxfId="44" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="22" operator="equal">
       <formula>$BR$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS2:BS15">
-    <cfRule type="cellIs" dxfId="43" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="21" operator="equal">
       <formula>$BS$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BH2:BH15">
-    <cfRule type="cellIs" dxfId="42" priority="2" operator="equal">
-      <formula>$BH$18</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BB2:BB15">
+  <conditionalFormatting sqref="BC2:BC15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$BB$18</formula>
+      <formula>$BC$18</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/predicciones.xlsx
+++ b/predicciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User710\Documents\Proyectos\Tabla-mundial-main\Tabla-mundial-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB506DF-1D10-444E-A756-D4AB176FE464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54067D26-8A0B-4C59-A789-25E8F02317E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="144">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -590,7 +590,987 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="91">
+  <dxfs count="231">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1242,10 +2222,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="90"/>
-      <tableStyleElement type="headerRow" dxfId="89"/>
-      <tableStyleElement type="firstRowStripe" dxfId="88"/>
-      <tableStyleElement type="secondRowStripe" dxfId="87"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="230"/>
+      <tableStyleElement type="headerRow" dxfId="229"/>
+      <tableStyleElement type="firstRowStripe" dxfId="228"/>
+      <tableStyleElement type="secondRowStripe" dxfId="227"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1337,10 +2317,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="86">
+    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="226">
       <calculatedColumnFormula>SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="85">
+    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="225">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2060,7 +3040,7 @@
       <c r="BT2" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="BU2" s="3" t="s">
+      <c r="BU2" s="8" t="s">
         <v>91</v>
       </c>
       <c r="BV2" s="3" t="s">
@@ -2071,7 +3051,7 @@
       </c>
       <c r="BX2" s="5">
         <f t="shared" ref="BX2:BX14" si="0">SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BY2" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2306,7 +3286,7 @@
       </c>
       <c r="BX3" s="5">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="BY3" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2541,7 +3521,7 @@
       </c>
       <c r="BX4" s="5">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BY4" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2776,7 +3756,7 @@
       </c>
       <c r="BX5" s="5">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BY5" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3011,7 +3991,7 @@
       </c>
       <c r="BX6" s="5">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BY6" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3246,7 +4226,7 @@
       </c>
       <c r="BX7" s="5">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BY7" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3481,7 +4461,7 @@
       </c>
       <c r="BX8" s="5">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BY8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3716,7 +4696,7 @@
       </c>
       <c r="BX9" s="5">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BY9" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3951,7 +4931,7 @@
       </c>
       <c r="BX10" s="5">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BY10" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4186,7 +5166,7 @@
       </c>
       <c r="BX11" s="5">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BY11" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4421,7 +5401,7 @@
       </c>
       <c r="BX12" s="5">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BY12" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4656,7 +5636,7 @@
       </c>
       <c r="BX13" s="5">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BY13" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4891,7 +5871,7 @@
       </c>
       <c r="BX14" s="5">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BY14" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5123,7 +6103,7 @@
       </c>
       <c r="BX15" s="5">
         <f>SUMPRODUCT((D15:BW15=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BY15" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5133,7 +6113,7 @@
     <row r="16" spans="1:77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="BX16" s="5"/>
     </row>
-    <row r="18" spans="1:71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>127</v>
       </c>
@@ -5254,233 +6234,265 @@
       <c r="BH18" t="s">
         <v>87</v>
       </c>
+      <c r="BI18" s="7" t="s">
+        <v>111</v>
+      </c>
       <c r="BL18" s="7" t="s">
         <v>76</v>
       </c>
       <c r="BM18" s="7" t="s">
         <v>89</v>
       </c>
+      <c r="BN18" s="7" t="s">
+        <v>88</v>
+      </c>
       <c r="BR18" s="7" t="s">
         <v>90</v>
       </c>
       <c r="BS18" t="s">
         <v>113</v>
+      </c>
+      <c r="BT18" t="s">
+        <v>76</v>
+      </c>
+      <c r="BU18" s="7" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D16">
-    <cfRule type="cellIs" dxfId="84" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="47" operator="equal">
       <formula>$D$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E16">
-    <cfRule type="cellIs" dxfId="83" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="46" operator="equal">
       <formula>$E$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F15">
-    <cfRule type="cellIs" dxfId="82" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="23" operator="equal">
       <formula>$F$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G15">
-    <cfRule type="cellIs" dxfId="81" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="20" operator="equal">
       <formula>$G$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J16">
-    <cfRule type="cellIs" dxfId="80" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="88" priority="45" operator="equal">
       <formula>$J$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K15">
-    <cfRule type="cellIs" dxfId="79" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="43" operator="equal">
       <formula>$K$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L15">
-    <cfRule type="cellIs" dxfId="78" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="22" operator="equal">
       <formula>$L$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M15">
-    <cfRule type="cellIs" dxfId="77" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="21" operator="equal">
       <formula>$M$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P15">
-    <cfRule type="cellIs" dxfId="76" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="42" operator="equal">
       <formula>$P$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q15">
-    <cfRule type="cellIs" dxfId="75" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="41" operator="equal">
       <formula>$Q$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R15">
-    <cfRule type="cellIs" dxfId="74" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="19" operator="equal">
       <formula>$R$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S15">
-    <cfRule type="cellIs" dxfId="73" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="18" operator="equal">
       <formula>$S$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V16">
-    <cfRule type="cellIs" dxfId="72" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="44" operator="equal">
       <formula>$V$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W15">
-    <cfRule type="cellIs" dxfId="71" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="40" operator="equal">
       <formula>$W$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X15">
-    <cfRule type="cellIs" dxfId="70" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="17" operator="equal">
       <formula>$X$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y15">
-    <cfRule type="cellIs" dxfId="69" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="16" operator="equal">
       <formula>$Y$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB15">
-    <cfRule type="cellIs" dxfId="68" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="39" operator="equal">
       <formula>$AB$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC15">
-    <cfRule type="cellIs" dxfId="67" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="37" operator="equal">
       <formula>$AC$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD15">
-    <cfRule type="cellIs" dxfId="66" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="15" operator="equal">
       <formula>$AD$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE15">
-    <cfRule type="cellIs" dxfId="65" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="13" operator="equal">
       <formula>$AE$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH15">
-    <cfRule type="cellIs" dxfId="64" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="38" operator="equal">
       <formula>$AH$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI15">
-    <cfRule type="cellIs" dxfId="63" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="36" operator="equal">
       <formula>$AI$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ2:AJ15">
-    <cfRule type="cellIs" dxfId="62" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="14" operator="equal">
       <formula>$AJ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK2:AK15">
-    <cfRule type="cellIs" dxfId="61" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="12" operator="equal">
       <formula>$AK$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN15">
-    <cfRule type="cellIs" dxfId="60" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="33" operator="equal">
       <formula>$AN$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO2:AO15">
-    <cfRule type="cellIs" dxfId="59" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="32" operator="equal">
       <formula>$AO$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP2:AP15">
-    <cfRule type="cellIs" dxfId="58" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="9" operator="equal">
       <formula>$AP$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ2:AQ15">
-    <cfRule type="cellIs" dxfId="57" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="8" operator="equal">
       <formula>$AQ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT15">
-    <cfRule type="cellIs" dxfId="56" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="35" operator="equal">
       <formula>$AT$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU15">
-    <cfRule type="cellIs" dxfId="55" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="34" operator="equal">
       <formula>$AU$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV2:AV15">
-    <cfRule type="cellIs" dxfId="54" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="11" operator="equal">
       <formula>$AV$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW2:AW15">
-    <cfRule type="cellIs" dxfId="53" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="10" operator="equal">
       <formula>$AW$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ2:AZ15">
-    <cfRule type="cellIs" dxfId="52" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="31" operator="equal">
       <formula>$AZ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA2:BA15">
-    <cfRule type="cellIs" dxfId="51" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="30" operator="equal">
       <formula>$BA$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB2:BB15">
-    <cfRule type="cellIs" dxfId="50" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="6" operator="equal">
       <formula>$BB$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="BC2:BC15">
+    <cfRule type="cellIs" dxfId="57" priority="5" operator="equal">
+      <formula>$BC$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="BF2:BF15">
-    <cfRule type="cellIs" dxfId="49" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="29" operator="equal">
       <formula>$BF$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG2:BG15">
-    <cfRule type="cellIs" dxfId="48" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="28" operator="equal">
       <formula>$BG$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BH2:BH15">
-    <cfRule type="cellIs" dxfId="47" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="7" operator="equal">
       <formula>$BH$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL2:BL15">
-    <cfRule type="cellIs" dxfId="46" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="27" operator="equal">
       <formula>$BL$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM2:BM15">
-    <cfRule type="cellIs" dxfId="45" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="24" operator="equal">
       <formula>$BM$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BR2:BR15">
-    <cfRule type="cellIs" dxfId="44" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="26" operator="equal">
       <formula>$BR$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS2:BS15">
-    <cfRule type="cellIs" dxfId="43" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="25" operator="equal">
       <formula>$BS$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BC2:BC15">
+  <conditionalFormatting sqref="BT2:BT15">
+    <cfRule type="cellIs" dxfId="49" priority="4" operator="equal">
+      <formula>$BT$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BU2:BU15">
+    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
+      <formula>$BU$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BN2:BN15">
+    <cfRule type="cellIs" dxfId="47" priority="2" operator="equal">
+      <formula>$BN$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BI2:BI15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$BC$18</formula>
+      <formula>$BI$18</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/predicciones.xlsx
+++ b/predicciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User710\Documents\Proyectos\Tabla-mundial-main\Tabla-mundial-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54067D26-8A0B-4C59-A789-25E8F02317E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2577D35-B03F-4BDE-90AA-DA9AC428E639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="144">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -590,917 +590,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="231">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="101">
     <dxf>
       <fill>
         <patternFill>
@@ -2222,10 +1312,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="230"/>
-      <tableStyleElement type="headerRow" dxfId="229"/>
-      <tableStyleElement type="firstRowStripe" dxfId="228"/>
-      <tableStyleElement type="secondRowStripe" dxfId="227"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="100"/>
+      <tableStyleElement type="headerRow" dxfId="99"/>
+      <tableStyleElement type="firstRowStripe" dxfId="98"/>
+      <tableStyleElement type="secondRowStripe" dxfId="97"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2317,10 +1407,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="226">
+    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="96">
       <calculatedColumnFormula>SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="225">
+    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="95">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3051,7 +2141,7 @@
       </c>
       <c r="BX2" s="5">
         <f t="shared" ref="BX2:BX14" si="0">SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BY2" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3286,7 +2376,7 @@
       </c>
       <c r="BX3" s="5">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BY3" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3521,7 +2611,7 @@
       </c>
       <c r="BX4" s="5">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BY4" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3756,7 +2846,7 @@
       </c>
       <c r="BX5" s="5">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BY5" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3991,7 +3081,7 @@
       </c>
       <c r="BX6" s="5">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BY6" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4226,7 +3316,7 @@
       </c>
       <c r="BX7" s="5">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BY7" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4461,7 +3551,7 @@
       </c>
       <c r="BX8" s="5">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BY8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4696,7 +3786,7 @@
       </c>
       <c r="BX9" s="5">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BY9" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4931,7 +4021,7 @@
       </c>
       <c r="BX10" s="5">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BY10" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5166,7 +4256,7 @@
       </c>
       <c r="BX11" s="5">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BY11" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5636,7 +4726,7 @@
       </c>
       <c r="BX13" s="5">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BY13" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5871,7 +4961,7 @@
       </c>
       <c r="BX14" s="5">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BY14" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6103,7 +5193,7 @@
       </c>
       <c r="BX15" s="5">
         <f>SUMPRODUCT((D15:BW15=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BY15" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6246,6 +5336,9 @@
       <c r="BN18" s="7" t="s">
         <v>88</v>
       </c>
+      <c r="BO18" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="BR18" s="7" t="s">
         <v>90</v>
       </c>
@@ -6261,238 +5354,243 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D16">
-    <cfRule type="cellIs" dxfId="92" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="94" priority="48" operator="equal">
       <formula>$D$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E16">
-    <cfRule type="cellIs" dxfId="91" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="47" operator="equal">
       <formula>$E$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F15">
-    <cfRule type="cellIs" dxfId="90" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="24" operator="equal">
       <formula>$F$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G15">
-    <cfRule type="cellIs" dxfId="89" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="21" operator="equal">
       <formula>$G$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J16">
-    <cfRule type="cellIs" dxfId="88" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="46" operator="equal">
       <formula>$J$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K15">
-    <cfRule type="cellIs" dxfId="87" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="44" operator="equal">
       <formula>$K$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L15">
-    <cfRule type="cellIs" dxfId="86" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="88" priority="23" operator="equal">
       <formula>$L$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M15">
-    <cfRule type="cellIs" dxfId="85" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="22" operator="equal">
       <formula>$M$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P15">
-    <cfRule type="cellIs" dxfId="84" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="43" operator="equal">
       <formula>$P$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q15">
-    <cfRule type="cellIs" dxfId="83" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="42" operator="equal">
       <formula>$Q$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R15">
-    <cfRule type="cellIs" dxfId="82" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="20" operator="equal">
       <formula>$R$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S15">
-    <cfRule type="cellIs" dxfId="81" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="19" operator="equal">
       <formula>$S$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V16">
-    <cfRule type="cellIs" dxfId="80" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="45" operator="equal">
       <formula>$V$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W15">
-    <cfRule type="cellIs" dxfId="79" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="41" operator="equal">
       <formula>$W$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X15">
-    <cfRule type="cellIs" dxfId="78" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="18" operator="equal">
       <formula>$X$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y15">
-    <cfRule type="cellIs" dxfId="77" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="17" operator="equal">
       <formula>$Y$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB15">
-    <cfRule type="cellIs" dxfId="76" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="40" operator="equal">
       <formula>$AB$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC15">
-    <cfRule type="cellIs" dxfId="75" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="38" operator="equal">
       <formula>$AC$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD15">
-    <cfRule type="cellIs" dxfId="74" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="16" operator="equal">
       <formula>$AD$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE15">
-    <cfRule type="cellIs" dxfId="73" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="14" operator="equal">
       <formula>$AE$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH15">
-    <cfRule type="cellIs" dxfId="72" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="39" operator="equal">
       <formula>$AH$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI15">
-    <cfRule type="cellIs" dxfId="71" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="37" operator="equal">
       <formula>$AI$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ2:AJ15">
-    <cfRule type="cellIs" dxfId="70" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="15" operator="equal">
       <formula>$AJ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK2:AK15">
-    <cfRule type="cellIs" dxfId="69" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="13" operator="equal">
       <formula>$AK$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN15">
-    <cfRule type="cellIs" dxfId="68" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="34" operator="equal">
       <formula>$AN$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO2:AO15">
-    <cfRule type="cellIs" dxfId="67" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="33" operator="equal">
       <formula>$AO$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP2:AP15">
-    <cfRule type="cellIs" dxfId="66" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="10" operator="equal">
       <formula>$AP$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ2:AQ15">
-    <cfRule type="cellIs" dxfId="65" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="9" operator="equal">
       <formula>$AQ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT15">
-    <cfRule type="cellIs" dxfId="64" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="36" operator="equal">
       <formula>$AT$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU15">
-    <cfRule type="cellIs" dxfId="63" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="35" operator="equal">
       <formula>$AU$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV2:AV15">
-    <cfRule type="cellIs" dxfId="62" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="12" operator="equal">
       <formula>$AV$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW2:AW15">
-    <cfRule type="cellIs" dxfId="61" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="11" operator="equal">
       <formula>$AW$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ2:AZ15">
-    <cfRule type="cellIs" dxfId="60" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="32" operator="equal">
       <formula>$AZ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA2:BA15">
-    <cfRule type="cellIs" dxfId="59" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="31" operator="equal">
       <formula>$BA$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB2:BB15">
-    <cfRule type="cellIs" dxfId="58" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="7" operator="equal">
       <formula>$BB$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BC2:BC15">
-    <cfRule type="cellIs" dxfId="57" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="6" operator="equal">
       <formula>$BC$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BF2:BF15">
-    <cfRule type="cellIs" dxfId="56" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="30" operator="equal">
       <formula>$BF$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG2:BG15">
-    <cfRule type="cellIs" dxfId="55" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="29" operator="equal">
       <formula>$BG$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BH2:BH15">
-    <cfRule type="cellIs" dxfId="54" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="8" operator="equal">
       <formula>$BH$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="BI2:BI15">
+    <cfRule type="cellIs" dxfId="55" priority="2" operator="equal">
+      <formula>$BI$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="BL2:BL15">
-    <cfRule type="cellIs" dxfId="53" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="28" operator="equal">
       <formula>$BL$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM2:BM15">
-    <cfRule type="cellIs" dxfId="52" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="25" operator="equal">
       <formula>$BM$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="BN2:BN15">
+    <cfRule type="cellIs" dxfId="52" priority="3" operator="equal">
+      <formula>$BN$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="BR2:BR15">
-    <cfRule type="cellIs" dxfId="51" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="27" operator="equal">
       <formula>$BR$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS2:BS15">
-    <cfRule type="cellIs" dxfId="50" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="26" operator="equal">
       <formula>$BS$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BT2:BT15">
-    <cfRule type="cellIs" dxfId="49" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="5" operator="equal">
       <formula>$BT$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BU2:BU15">
-    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="4" operator="equal">
       <formula>$BU$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BN2:BN15">
-    <cfRule type="cellIs" dxfId="47" priority="2" operator="equal">
-      <formula>$BN$18</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BI2:BI15">
+  <conditionalFormatting sqref="BO2:BO15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$BI$18</formula>
+      <formula>$BO$18</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/predicciones.xlsx
+++ b/predicciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User710\Documents\Proyectos\Tabla-mundial-main\Tabla-mundial-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2577D35-B03F-4BDE-90AA-DA9AC428E639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{859FB5AF-234A-4364-A840-D4B863CF173D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="144">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -590,7 +590,1092 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="101">
+  <dxfs count="256">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1312,10 +2397,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="100"/>
-      <tableStyleElement type="headerRow" dxfId="99"/>
-      <tableStyleElement type="firstRowStripe" dxfId="98"/>
-      <tableStyleElement type="secondRowStripe" dxfId="97"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="255"/>
+      <tableStyleElement type="headerRow" dxfId="254"/>
+      <tableStyleElement type="firstRowStripe" dxfId="253"/>
+      <tableStyleElement type="secondRowStripe" dxfId="252"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1407,10 +2492,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="96">
+    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="251">
       <calculatedColumnFormula>SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="95">
+    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="250">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2376,7 +3461,7 @@
       </c>
       <c r="BX3" s="5">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY3" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2611,7 +3696,7 @@
       </c>
       <c r="BX4" s="5">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BY4" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -2846,7 +3931,7 @@
       </c>
       <c r="BX5" s="5">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BY5" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3081,7 +4166,7 @@
       </c>
       <c r="BX6" s="5">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BY6" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3316,7 +4401,7 @@
       </c>
       <c r="BX7" s="5">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BY7" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3551,7 +4636,7 @@
       </c>
       <c r="BX8" s="5">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BY8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3786,7 +4871,7 @@
       </c>
       <c r="BX9" s="5">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BY9" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4021,7 +5106,7 @@
       </c>
       <c r="BX10" s="5">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="BY10" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4256,7 +5341,7 @@
       </c>
       <c r="BX11" s="5">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BY11" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4491,7 +5576,7 @@
       </c>
       <c r="BX12" s="5">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="BY12" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4726,7 +5811,7 @@
       </c>
       <c r="BX13" s="5">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BY13" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4961,7 +6046,7 @@
       </c>
       <c r="BX14" s="5">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BY14" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5193,7 +6278,7 @@
       </c>
       <c r="BX15" s="5">
         <f>SUMPRODUCT((D15:BW15=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="BY15" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5231,6 +6316,12 @@
       <c r="M18" s="7" t="s">
         <v>95</v>
       </c>
+      <c r="N18" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="O18" s="7" t="s">
+        <v>118</v>
+      </c>
       <c r="P18" t="s">
         <v>76</v>
       </c>
@@ -5242,6 +6333,12 @@
       </c>
       <c r="S18" t="s">
         <v>78</v>
+      </c>
+      <c r="T18" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="U18" s="7" t="s">
+        <v>98</v>
       </c>
       <c r="V18" t="s">
         <v>101</v>
@@ -5354,243 +6451,263 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D16">
-    <cfRule type="cellIs" dxfId="94" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="102" priority="52" operator="equal">
       <formula>$D$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E16">
-    <cfRule type="cellIs" dxfId="93" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="101" priority="51" operator="equal">
       <formula>$E$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F15">
-    <cfRule type="cellIs" dxfId="92" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="28" operator="equal">
       <formula>$F$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G15">
-    <cfRule type="cellIs" dxfId="91" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="99" priority="25" operator="equal">
       <formula>$G$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J16">
-    <cfRule type="cellIs" dxfId="90" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="98" priority="50" operator="equal">
       <formula>$J$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K15">
-    <cfRule type="cellIs" dxfId="89" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="97" priority="48" operator="equal">
       <formula>$K$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L15">
-    <cfRule type="cellIs" dxfId="88" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="27" operator="equal">
       <formula>$L$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M15">
-    <cfRule type="cellIs" dxfId="87" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="95" priority="26" operator="equal">
       <formula>$M$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P15">
-    <cfRule type="cellIs" dxfId="86" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="94" priority="47" operator="equal">
       <formula>$P$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q15">
-    <cfRule type="cellIs" dxfId="85" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="46" operator="equal">
       <formula>$Q$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R15">
-    <cfRule type="cellIs" dxfId="84" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="24" operator="equal">
       <formula>$R$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S15">
-    <cfRule type="cellIs" dxfId="83" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="23" operator="equal">
       <formula>$S$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V16">
-    <cfRule type="cellIs" dxfId="82" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="49" operator="equal">
       <formula>$V$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W15">
-    <cfRule type="cellIs" dxfId="81" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="45" operator="equal">
       <formula>$W$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X15">
-    <cfRule type="cellIs" dxfId="80" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="88" priority="22" operator="equal">
       <formula>$X$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y15">
-    <cfRule type="cellIs" dxfId="79" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="21" operator="equal">
       <formula>$Y$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB15">
-    <cfRule type="cellIs" dxfId="78" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="44" operator="equal">
       <formula>$AB$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC15">
-    <cfRule type="cellIs" dxfId="77" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="42" operator="equal">
       <formula>$AC$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD15">
-    <cfRule type="cellIs" dxfId="76" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="20" operator="equal">
       <formula>$AD$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE15">
-    <cfRule type="cellIs" dxfId="75" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="18" operator="equal">
       <formula>$AE$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH15">
-    <cfRule type="cellIs" dxfId="74" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="43" operator="equal">
       <formula>$AH$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI15">
-    <cfRule type="cellIs" dxfId="73" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="41" operator="equal">
       <formula>$AI$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ2:AJ15">
-    <cfRule type="cellIs" dxfId="72" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="19" operator="equal">
       <formula>$AJ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK2:AK15">
-    <cfRule type="cellIs" dxfId="71" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="17" operator="equal">
       <formula>$AK$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN15">
-    <cfRule type="cellIs" dxfId="70" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="38" operator="equal">
       <formula>$AN$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO2:AO15">
-    <cfRule type="cellIs" dxfId="69" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="37" operator="equal">
       <formula>$AO$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP2:AP15">
-    <cfRule type="cellIs" dxfId="68" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="14" operator="equal">
       <formula>$AP$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ2:AQ15">
-    <cfRule type="cellIs" dxfId="67" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="13" operator="equal">
       <formula>$AQ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT15">
-    <cfRule type="cellIs" dxfId="66" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="40" operator="equal">
       <formula>$AT$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU15">
-    <cfRule type="cellIs" dxfId="65" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="39" operator="equal">
       <formula>$AU$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV2:AV15">
-    <cfRule type="cellIs" dxfId="64" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="16" operator="equal">
       <formula>$AV$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW2:AW15">
-    <cfRule type="cellIs" dxfId="63" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="15" operator="equal">
       <formula>$AW$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ2:AZ15">
-    <cfRule type="cellIs" dxfId="62" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="36" operator="equal">
       <formula>$AZ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA2:BA15">
-    <cfRule type="cellIs" dxfId="61" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="35" operator="equal">
       <formula>$BA$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB2:BB15">
-    <cfRule type="cellIs" dxfId="60" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="11" operator="equal">
       <formula>$BB$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BC2:BC15">
-    <cfRule type="cellIs" dxfId="59" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="10" operator="equal">
       <formula>$BC$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BF2:BF15">
-    <cfRule type="cellIs" dxfId="58" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="34" operator="equal">
       <formula>$BF$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG2:BG15">
-    <cfRule type="cellIs" dxfId="57" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="33" operator="equal">
       <formula>$BG$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BH2:BH15">
-    <cfRule type="cellIs" dxfId="56" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="12" operator="equal">
       <formula>$BH$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI2:BI15">
-    <cfRule type="cellIs" dxfId="55" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="6" operator="equal">
       <formula>$BI$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL2:BL15">
-    <cfRule type="cellIs" dxfId="54" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="32" operator="equal">
       <formula>$BL$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM2:BM15">
-    <cfRule type="cellIs" dxfId="53" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="29" operator="equal">
       <formula>$BM$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BN2:BN15">
-    <cfRule type="cellIs" dxfId="52" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="7" operator="equal">
       <formula>$BN$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="BO2:BO15">
+    <cfRule type="cellIs" dxfId="59" priority="5" operator="equal">
+      <formula>$BO$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="BR2:BR15">
-    <cfRule type="cellIs" dxfId="51" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="31" operator="equal">
       <formula>$BR$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS2:BS15">
-    <cfRule type="cellIs" dxfId="50" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="30" operator="equal">
       <formula>$BS$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BT2:BT15">
-    <cfRule type="cellIs" dxfId="49" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="9" operator="equal">
       <formula>$BT$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BU2:BU15">
-    <cfRule type="cellIs" dxfId="48" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="8" operator="equal">
       <formula>$BU$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BO2:BO15">
+  <conditionalFormatting sqref="N2:N15">
+    <cfRule type="cellIs" dxfId="54" priority="4" operator="equal">
+      <formula>$N$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O2:O15">
+    <cfRule type="cellIs" dxfId="53" priority="3" operator="equal">
+      <formula>$O$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T15">
+    <cfRule type="cellIs" dxfId="52" priority="2" operator="equal">
+      <formula>$T$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U2:U15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$BO$18</formula>
+      <formula>$U$18</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/predicciones.xlsx
+++ b/predicciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User710\Documents\Proyectos\Tabla-mundial-main\Tabla-mundial-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{859FB5AF-234A-4364-A840-D4B863CF173D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D930601A-2A07-42AC-B068-C85785AD3841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1171" uniqueCount="144">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -590,7 +590,952 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="256">
+  <dxfs count="391">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2397,10 +3342,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="255"/>
-      <tableStyleElement type="headerRow" dxfId="254"/>
-      <tableStyleElement type="firstRowStripe" dxfId="253"/>
-      <tableStyleElement type="secondRowStripe" dxfId="252"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="390"/>
+      <tableStyleElement type="headerRow" dxfId="389"/>
+      <tableStyleElement type="firstRowStripe" dxfId="388"/>
+      <tableStyleElement type="secondRowStripe" dxfId="387"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2492,10 +3437,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="251">
+    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="386">
       <calculatedColumnFormula>SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="250">
+    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="385">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3226,7 +4171,7 @@
       </c>
       <c r="BX2" s="5">
         <f t="shared" ref="BX2:BX14" si="0">SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BY2" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3461,7 +4406,7 @@
       </c>
       <c r="BX3" s="5">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BY3" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3696,7 +4641,7 @@
       </c>
       <c r="BX4" s="5">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BY4" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -3931,7 +4876,7 @@
       </c>
       <c r="BX5" s="5">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="BY5" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4166,7 +5111,7 @@
       </c>
       <c r="BX6" s="5">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BY6" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4401,7 +5346,7 @@
       </c>
       <c r="BX7" s="5">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BY7" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4636,7 +5581,7 @@
       </c>
       <c r="BX8" s="5">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="BY8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4871,7 +5816,7 @@
       </c>
       <c r="BX9" s="5">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BY9" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5106,7 +6051,7 @@
       </c>
       <c r="BX10" s="5">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="BY10" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5341,7 +6286,7 @@
       </c>
       <c r="BX11" s="5">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BY11" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5576,7 +6521,7 @@
       </c>
       <c r="BX12" s="5">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="BY12" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5811,7 +6756,7 @@
       </c>
       <c r="BX13" s="5">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BY13" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6046,7 +6991,7 @@
       </c>
       <c r="BX14" s="5">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BY14" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6278,7 +7223,7 @@
       </c>
       <c r="BX15" s="5">
         <f>SUMPRODUCT((D15:BW15=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="BY15" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6304,6 +7249,12 @@
       <c r="G18" s="7" t="s">
         <v>77</v>
       </c>
+      <c r="H18" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>115</v>
+      </c>
       <c r="J18" t="s">
         <v>76</v>
       </c>
@@ -6364,6 +7315,12 @@
       <c r="AE18" t="s">
         <v>76</v>
       </c>
+      <c r="AF18" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="AG18" s="7" t="s">
+        <v>81</v>
+      </c>
       <c r="AH18" s="7" t="s">
         <v>76</v>
       </c>
@@ -6375,6 +7332,12 @@
       </c>
       <c r="AK18" s="7" t="s">
         <v>104</v>
+      </c>
+      <c r="AL18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="AM18" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="AN18" s="7" t="s">
         <v>76</v>
@@ -6451,263 +7414,293 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D16">
-    <cfRule type="cellIs" dxfId="102" priority="52" operator="equal">
+    <cfRule type="cellIs" dxfId="114" priority="58" operator="equal">
       <formula>$D$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E16">
-    <cfRule type="cellIs" dxfId="101" priority="51" operator="equal">
+    <cfRule type="cellIs" dxfId="113" priority="57" operator="equal">
       <formula>$E$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F15">
-    <cfRule type="cellIs" dxfId="100" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="112" priority="34" operator="equal">
       <formula>$F$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G15">
-    <cfRule type="cellIs" dxfId="99" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="111" priority="31" operator="equal">
       <formula>$G$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J16">
-    <cfRule type="cellIs" dxfId="98" priority="50" operator="equal">
+    <cfRule type="cellIs" dxfId="110" priority="56" operator="equal">
       <formula>$J$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K15">
-    <cfRule type="cellIs" dxfId="97" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="109" priority="54" operator="equal">
       <formula>$K$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L15">
-    <cfRule type="cellIs" dxfId="96" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="108" priority="33" operator="equal">
       <formula>$L$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M15">
-    <cfRule type="cellIs" dxfId="95" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="107" priority="32" operator="equal">
       <formula>$M$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N15">
+    <cfRule type="cellIs" dxfId="106" priority="10" operator="equal">
+      <formula>$N$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O2:O15">
+    <cfRule type="cellIs" dxfId="105" priority="9" operator="equal">
+      <formula>$O$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="P2:P15">
-    <cfRule type="cellIs" dxfId="94" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="104" priority="53" operator="equal">
       <formula>$P$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q15">
-    <cfRule type="cellIs" dxfId="93" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="103" priority="52" operator="equal">
       <formula>$Q$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R15">
-    <cfRule type="cellIs" dxfId="92" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="102" priority="30" operator="equal">
       <formula>$R$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S15">
-    <cfRule type="cellIs" dxfId="91" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="101" priority="29" operator="equal">
       <formula>$S$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T15">
+    <cfRule type="cellIs" dxfId="100" priority="8" operator="equal">
+      <formula>$T$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U2:U15">
+    <cfRule type="cellIs" dxfId="99" priority="7" operator="equal">
+      <formula>$U$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="V2:V16">
-    <cfRule type="cellIs" dxfId="90" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="98" priority="55" operator="equal">
       <formula>$V$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W15">
-    <cfRule type="cellIs" dxfId="89" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="97" priority="51" operator="equal">
       <formula>$W$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X15">
-    <cfRule type="cellIs" dxfId="88" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="28" operator="equal">
       <formula>$X$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y15">
-    <cfRule type="cellIs" dxfId="87" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="95" priority="27" operator="equal">
       <formula>$Y$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB15">
-    <cfRule type="cellIs" dxfId="86" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="94" priority="50" operator="equal">
       <formula>$AB$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC15">
-    <cfRule type="cellIs" dxfId="85" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="48" operator="equal">
       <formula>$AC$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD15">
-    <cfRule type="cellIs" dxfId="84" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="26" operator="equal">
       <formula>$AD$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE15">
-    <cfRule type="cellIs" dxfId="83" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="24" operator="equal">
       <formula>$AE$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH15">
-    <cfRule type="cellIs" dxfId="82" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="49" operator="equal">
       <formula>$AH$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI15">
-    <cfRule type="cellIs" dxfId="81" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="47" operator="equal">
       <formula>$AI$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ2:AJ15">
-    <cfRule type="cellIs" dxfId="80" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="88" priority="25" operator="equal">
       <formula>$AJ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK2:AK15">
-    <cfRule type="cellIs" dxfId="79" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="23" operator="equal">
       <formula>$AK$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN15">
-    <cfRule type="cellIs" dxfId="78" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="44" operator="equal">
       <formula>$AN$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO2:AO15">
-    <cfRule type="cellIs" dxfId="77" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="43" operator="equal">
       <formula>$AO$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP2:AP15">
-    <cfRule type="cellIs" dxfId="76" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="20" operator="equal">
       <formula>$AP$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ2:AQ15">
-    <cfRule type="cellIs" dxfId="75" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="19" operator="equal">
       <formula>$AQ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT15">
-    <cfRule type="cellIs" dxfId="74" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="46" operator="equal">
       <formula>$AT$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU15">
-    <cfRule type="cellIs" dxfId="73" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="45" operator="equal">
       <formula>$AU$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV2:AV15">
-    <cfRule type="cellIs" dxfId="72" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="22" operator="equal">
       <formula>$AV$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW2:AW15">
-    <cfRule type="cellIs" dxfId="71" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="21" operator="equal">
       <formula>$AW$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ2:AZ15">
-    <cfRule type="cellIs" dxfId="70" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="42" operator="equal">
       <formula>$AZ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA2:BA15">
-    <cfRule type="cellIs" dxfId="69" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="41" operator="equal">
       <formula>$BA$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB2:BB15">
-    <cfRule type="cellIs" dxfId="68" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="17" operator="equal">
       <formula>$BB$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BC2:BC15">
-    <cfRule type="cellIs" dxfId="67" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="16" operator="equal">
       <formula>$BC$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BF2:BF15">
-    <cfRule type="cellIs" dxfId="66" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="40" operator="equal">
       <formula>$BF$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG2:BG15">
-    <cfRule type="cellIs" dxfId="65" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="39" operator="equal">
       <formula>$BG$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BH2:BH15">
-    <cfRule type="cellIs" dxfId="64" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="18" operator="equal">
       <formula>$BH$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI2:BI15">
-    <cfRule type="cellIs" dxfId="63" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="12" operator="equal">
       <formula>$BI$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL2:BL15">
-    <cfRule type="cellIs" dxfId="62" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="38" operator="equal">
       <formula>$BL$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM2:BM15">
-    <cfRule type="cellIs" dxfId="61" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="35" operator="equal">
       <formula>$BM$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BN2:BN15">
-    <cfRule type="cellIs" dxfId="60" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="13" operator="equal">
       <formula>$BN$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BO2:BO15">
-    <cfRule type="cellIs" dxfId="59" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="11" operator="equal">
       <formula>$BO$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BR2:BR15">
-    <cfRule type="cellIs" dxfId="58" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="37" operator="equal">
       <formula>$BR$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS2:BS15">
-    <cfRule type="cellIs" dxfId="57" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="36" operator="equal">
       <formula>$BS$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BT2:BT15">
-    <cfRule type="cellIs" dxfId="56" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="15" operator="equal">
       <formula>$BT$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BU2:BU15">
-    <cfRule type="cellIs" dxfId="55" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="14" operator="equal">
       <formula>$BU$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N15">
-    <cfRule type="cellIs" dxfId="54" priority="4" operator="equal">
-      <formula>$N$18</formula>
+  <conditionalFormatting sqref="H2:H15">
+    <cfRule type="cellIs" dxfId="62" priority="6" operator="equal">
+      <formula>$H$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O15">
-    <cfRule type="cellIs" dxfId="53" priority="3" operator="equal">
-      <formula>$O$18</formula>
+  <conditionalFormatting sqref="I2:I15">
+    <cfRule type="cellIs" dxfId="61" priority="5" operator="equal">
+      <formula>$I$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T15">
-    <cfRule type="cellIs" dxfId="52" priority="2" operator="equal">
-      <formula>$T$18</formula>
+  <conditionalFormatting sqref="AF2:AF15">
+    <cfRule type="cellIs" dxfId="60" priority="4" operator="equal">
+      <formula>$AF$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U15">
+  <conditionalFormatting sqref="AG2:AG15">
+    <cfRule type="cellIs" dxfId="59" priority="3" operator="equal">
+      <formula>$AG$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL2:AL15">
+    <cfRule type="cellIs" dxfId="58" priority="2" operator="equal">
+      <formula>$AL$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AM2:AM15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$U$18</formula>
+      <formula>$AM$18</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/predicciones.xlsx
+++ b/predicciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User710\Documents\Proyectos\Tabla-mundial-main\Tabla-mundial-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D930601A-2A07-42AC-B068-C85785AD3841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{508A1868-D463-4499-8A2C-179183E43100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1171" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="144">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -590,7 +590,231 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="391">
+  <dxfs count="564">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1048,2009 +1272,2996 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
+        <patternFill patternType="solid">
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <bgColor theme="7"/>
         </patternFill>
       </fill>
@@ -3342,10 +4553,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="390"/>
-      <tableStyleElement type="headerRow" dxfId="389"/>
-      <tableStyleElement type="firstRowStripe" dxfId="388"/>
-      <tableStyleElement type="secondRowStripe" dxfId="387"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="563"/>
+      <tableStyleElement type="headerRow" dxfId="562"/>
+      <tableStyleElement type="firstRowStripe" dxfId="561"/>
+      <tableStyleElement type="secondRowStripe" dxfId="560"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3437,10 +4648,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="386">
+    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="559">
       <calculatedColumnFormula>SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="385">
+    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="558">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4171,7 +5382,7 @@
       </c>
       <c r="BX2" s="5">
         <f t="shared" ref="BX2:BX14" si="0">SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BY2" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4406,7 +5617,7 @@
       </c>
       <c r="BX3" s="5">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY3" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4641,7 +5852,7 @@
       </c>
       <c r="BX4" s="5">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BY4" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -4876,7 +6087,7 @@
       </c>
       <c r="BX5" s="5">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="BY5" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5111,7 +6322,7 @@
       </c>
       <c r="BX6" s="5">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BY6" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5346,7 +6557,7 @@
       </c>
       <c r="BX7" s="5">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BY7" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5581,7 +6792,7 @@
       </c>
       <c r="BX8" s="5">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="BY8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5816,7 +7027,7 @@
       </c>
       <c r="BX9" s="5">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="BY9" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6051,7 +7262,7 @@
       </c>
       <c r="BX10" s="5">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="BY10" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6286,7 +7497,7 @@
       </c>
       <c r="BX11" s="5">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="BY11" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6521,7 +7732,7 @@
       </c>
       <c r="BX12" s="5">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="BY12" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6756,7 +7967,7 @@
       </c>
       <c r="BX13" s="5">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BY13" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6991,7 +8202,7 @@
       </c>
       <c r="BX14" s="5">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BY14" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -7223,7 +8434,7 @@
       </c>
       <c r="BX15" s="5">
         <f>SUMPRODUCT((D15:BW15=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="BY15" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -7303,6 +8514,12 @@
       <c r="Y18" s="7" t="s">
         <v>79</v>
       </c>
+      <c r="Z18" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="AA18" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="AB18" s="7" t="s">
         <v>80</v>
       </c>
@@ -7351,6 +8568,12 @@
       <c r="AQ18" s="7" t="s">
         <v>106</v>
       </c>
+      <c r="AR18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="AS18" s="7" t="s">
+        <v>83</v>
+      </c>
       <c r="AT18" t="s">
         <v>76</v>
       </c>
@@ -7363,6 +8586,12 @@
       <c r="AW18" t="s">
         <v>76</v>
       </c>
+      <c r="AX18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="AY18" s="7" t="s">
+        <v>107</v>
+      </c>
       <c r="AZ18" t="s">
         <v>85</v>
       </c>
@@ -7374,6 +8603,12 @@
       </c>
       <c r="BC18" s="7" t="s">
         <v>109</v>
+      </c>
+      <c r="BD18" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="BE18" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="BF18" s="7" t="s">
         <v>87</v>
@@ -7414,293 +8649,333 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D16">
-    <cfRule type="cellIs" dxfId="114" priority="58" operator="equal">
+    <cfRule type="cellIs" dxfId="130" priority="66" operator="equal">
       <formula>$D$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E16">
-    <cfRule type="cellIs" dxfId="113" priority="57" operator="equal">
+    <cfRule type="cellIs" dxfId="129" priority="65" operator="equal">
       <formula>$E$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F15">
-    <cfRule type="cellIs" dxfId="112" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="128" priority="42" operator="equal">
       <formula>$F$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G15">
-    <cfRule type="cellIs" dxfId="111" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="127" priority="39" operator="equal">
       <formula>$G$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H15">
+    <cfRule type="cellIs" dxfId="126" priority="14" operator="equal">
+      <formula>$H$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I15">
+    <cfRule type="cellIs" dxfId="125" priority="13" operator="equal">
+      <formula>$I$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J2:J16">
-    <cfRule type="cellIs" dxfId="110" priority="56" operator="equal">
+    <cfRule type="cellIs" dxfId="124" priority="64" operator="equal">
       <formula>$J$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K15">
-    <cfRule type="cellIs" dxfId="109" priority="54" operator="equal">
+    <cfRule type="cellIs" dxfId="123" priority="62" operator="equal">
       <formula>$K$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L15">
-    <cfRule type="cellIs" dxfId="108" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="122" priority="41" operator="equal">
       <formula>$L$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M15">
-    <cfRule type="cellIs" dxfId="107" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="121" priority="40" operator="equal">
       <formula>$M$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N15">
-    <cfRule type="cellIs" dxfId="106" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="120" priority="18" operator="equal">
       <formula>$N$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O15">
-    <cfRule type="cellIs" dxfId="105" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="119" priority="17" operator="equal">
       <formula>$O$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P15">
-    <cfRule type="cellIs" dxfId="104" priority="53" operator="equal">
+    <cfRule type="cellIs" dxfId="118" priority="61" operator="equal">
       <formula>$P$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q15">
-    <cfRule type="cellIs" dxfId="103" priority="52" operator="equal">
+    <cfRule type="cellIs" dxfId="117" priority="60" operator="equal">
       <formula>$Q$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R15">
-    <cfRule type="cellIs" dxfId="102" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="116" priority="38" operator="equal">
       <formula>$R$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S15">
-    <cfRule type="cellIs" dxfId="101" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="115" priority="37" operator="equal">
       <formula>$S$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:T15">
-    <cfRule type="cellIs" dxfId="100" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="114" priority="16" operator="equal">
       <formula>$T$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U15">
-    <cfRule type="cellIs" dxfId="99" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="113" priority="15" operator="equal">
       <formula>$U$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V16">
-    <cfRule type="cellIs" dxfId="98" priority="55" operator="equal">
+    <cfRule type="cellIs" dxfId="112" priority="63" operator="equal">
       <formula>$V$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W15">
-    <cfRule type="cellIs" dxfId="97" priority="51" operator="equal">
+    <cfRule type="cellIs" dxfId="111" priority="59" operator="equal">
       <formula>$W$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X15">
-    <cfRule type="cellIs" dxfId="96" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="110" priority="36" operator="equal">
       <formula>$X$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y15">
-    <cfRule type="cellIs" dxfId="95" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="109" priority="35" operator="equal">
       <formula>$Y$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB15">
-    <cfRule type="cellIs" dxfId="94" priority="50" operator="equal">
+    <cfRule type="cellIs" dxfId="108" priority="58" operator="equal">
       <formula>$AB$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC15">
-    <cfRule type="cellIs" dxfId="93" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="107" priority="56" operator="equal">
       <formula>$AC$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD15">
-    <cfRule type="cellIs" dxfId="92" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="106" priority="34" operator="equal">
       <formula>$AD$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE15">
-    <cfRule type="cellIs" dxfId="91" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="105" priority="32" operator="equal">
       <formula>$AE$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AF2:AF15">
+    <cfRule type="cellIs" dxfId="104" priority="12" operator="equal">
+      <formula>$AF$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG2:AG15">
+    <cfRule type="cellIs" dxfId="103" priority="11" operator="equal">
+      <formula>$AG$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH15">
-    <cfRule type="cellIs" dxfId="90" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="102" priority="57" operator="equal">
       <formula>$AH$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI15">
-    <cfRule type="cellIs" dxfId="89" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="101" priority="55" operator="equal">
       <formula>$AI$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ2:AJ15">
-    <cfRule type="cellIs" dxfId="88" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="33" operator="equal">
       <formula>$AJ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK2:AK15">
-    <cfRule type="cellIs" dxfId="87" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="99" priority="31" operator="equal">
       <formula>$AK$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AL2:AL15">
+    <cfRule type="cellIs" dxfId="98" priority="10" operator="equal">
+      <formula>$AL$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AM2:AM15">
+    <cfRule type="cellIs" dxfId="97" priority="9" operator="equal">
+      <formula>$AM$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN15">
-    <cfRule type="cellIs" dxfId="86" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="52" operator="equal">
       <formula>$AN$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO2:AO15">
-    <cfRule type="cellIs" dxfId="85" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="95" priority="51" operator="equal">
       <formula>$AO$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP2:AP15">
-    <cfRule type="cellIs" dxfId="84" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="94" priority="28" operator="equal">
       <formula>$AP$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ2:AQ15">
-    <cfRule type="cellIs" dxfId="83" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="27" operator="equal">
       <formula>$AQ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT15">
-    <cfRule type="cellIs" dxfId="82" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="54" operator="equal">
       <formula>$AT$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU15">
-    <cfRule type="cellIs" dxfId="81" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="53" operator="equal">
       <formula>$AU$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV2:AV15">
-    <cfRule type="cellIs" dxfId="80" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="30" operator="equal">
       <formula>$AV$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW2:AW15">
-    <cfRule type="cellIs" dxfId="79" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="29" operator="equal">
       <formula>$AW$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ2:AZ15">
-    <cfRule type="cellIs" dxfId="78" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="88" priority="50" operator="equal">
       <formula>$AZ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA2:BA15">
-    <cfRule type="cellIs" dxfId="77" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="49" operator="equal">
       <formula>$BA$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB2:BB15">
-    <cfRule type="cellIs" dxfId="76" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="25" operator="equal">
       <formula>$BB$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BC2:BC15">
-    <cfRule type="cellIs" dxfId="75" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="24" operator="equal">
       <formula>$BC$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BF2:BF15">
-    <cfRule type="cellIs" dxfId="74" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="48" operator="equal">
       <formula>$BF$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG2:BG15">
-    <cfRule type="cellIs" dxfId="73" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="47" operator="equal">
       <formula>$BG$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BH2:BH15">
-    <cfRule type="cellIs" dxfId="72" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="26" operator="equal">
       <formula>$BH$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI2:BI15">
-    <cfRule type="cellIs" dxfId="71" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="20" operator="equal">
       <formula>$BI$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL2:BL15">
-    <cfRule type="cellIs" dxfId="70" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="46" operator="equal">
       <formula>$BL$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM2:BM15">
-    <cfRule type="cellIs" dxfId="69" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="43" operator="equal">
       <formula>$BM$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BN2:BN15">
-    <cfRule type="cellIs" dxfId="68" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="21" operator="equal">
       <formula>$BN$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BO2:BO15">
-    <cfRule type="cellIs" dxfId="67" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="19" operator="equal">
       <formula>$BO$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BR2:BR15">
-    <cfRule type="cellIs" dxfId="66" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="45" operator="equal">
       <formula>$BR$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS2:BS15">
-    <cfRule type="cellIs" dxfId="65" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="44" operator="equal">
       <formula>$BS$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BT2:BT15">
-    <cfRule type="cellIs" dxfId="64" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="23" operator="equal">
       <formula>$BT$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BU2:BU15">
-    <cfRule type="cellIs" dxfId="63" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="22" operator="equal">
       <formula>$BU$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H15">
-    <cfRule type="cellIs" dxfId="62" priority="6" operator="equal">
-      <formula>$H$18</formula>
+  <conditionalFormatting sqref="Z2:Z15">
+    <cfRule type="cellIs" dxfId="72" priority="8" operator="equal">
+      <formula>$Z$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I15">
-    <cfRule type="cellIs" dxfId="61" priority="5" operator="equal">
-      <formula>$I$18</formula>
+  <conditionalFormatting sqref="AA2:AA15">
+    <cfRule type="cellIs" dxfId="71" priority="7" operator="equal">
+      <formula>$AA$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF2:AF15">
-    <cfRule type="cellIs" dxfId="60" priority="4" operator="equal">
-      <formula>$AF$18</formula>
+  <conditionalFormatting sqref="AR2:AR15">
+    <cfRule type="cellIs" dxfId="70" priority="6" operator="equal">
+      <formula>$AR$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG2:AG15">
-    <cfRule type="cellIs" dxfId="59" priority="3" operator="equal">
-      <formula>$AG$18</formula>
+  <conditionalFormatting sqref="AS2:AS15">
+    <cfRule type="cellIs" dxfId="69" priority="5" operator="equal">
+      <formula>$AS$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL2:AL15">
-    <cfRule type="cellIs" dxfId="58" priority="2" operator="equal">
-      <formula>$AL$18</formula>
+  <conditionalFormatting sqref="AY2:AY15">
+    <cfRule type="cellIs" dxfId="68" priority="4" operator="equal">
+      <formula>$AY$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AM2:AM15">
+  <conditionalFormatting sqref="AX2:AX16">
+    <cfRule type="cellIs" dxfId="67" priority="3" operator="equal">
+      <formula>$AX$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BD2:BD15">
+    <cfRule type="cellIs" dxfId="66" priority="2" operator="equal">
+      <formula>$BD$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BE2:BE15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$AM$18</formula>
+      <formula>$BE$18</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/predicciones.xlsx
+++ b/predicciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User710\Documents\Proyectos\Tabla-mundial-main\Tabla-mundial-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{508A1868-D463-4499-8A2C-179183E43100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A5957A0-AF43-454A-A83D-21C7DD5DA407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1185" uniqueCount="144">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -590,7 +590,35 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="564">
+  <dxfs count="489">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1272,6 +1300,48 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill patternType="solid">
           <bgColor theme="7"/>
         </patternFill>
@@ -1720,6 +1790,48 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill patternType="solid">
           <bgColor theme="7"/>
         </patternFill>
@@ -2161,6 +2273,48 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill patternType="solid">
           <bgColor theme="7"/>
         </patternFill>
@@ -2595,6 +2749,48 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill patternType="solid">
           <bgColor theme="7"/>
         </patternFill>
@@ -3022,6 +3218,48 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill patternType="solid">
           <bgColor theme="7"/>
         </patternFill>
@@ -3442,6 +3680,48 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill patternType="solid">
           <bgColor theme="7"/>
         </patternFill>
@@ -3457,811 +3737,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <bgColor theme="7"/>
         </patternFill>
       </fill>
@@ -4553,10 +4028,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="563"/>
-      <tableStyleElement type="headerRow" dxfId="562"/>
-      <tableStyleElement type="firstRowStripe" dxfId="561"/>
-      <tableStyleElement type="secondRowStripe" dxfId="560"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="488"/>
+      <tableStyleElement type="headerRow" dxfId="487"/>
+      <tableStyleElement type="firstRowStripe" dxfId="486"/>
+      <tableStyleElement type="secondRowStripe" dxfId="485"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -4648,10 +4123,10 @@
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0000-000049000000}" name="Panamá - Croacia"/>
     <tableColumn id="74" xr3:uid="{00000000-0010-0000-0000-00004A000000}" name="Fecha 3:_x000a_Panamá - Inglaterra"/>
     <tableColumn id="75" xr3:uid="{00000000-0010-0000-0000-00004B000000}" name="Croacia - Ghana"/>
-    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="559">
+    <tableColumn id="76" xr3:uid="{D19EB80B-3773-43EA-9F95-F2BFBDC333FB}" name="Puntos" dataDxfId="484">
       <calculatedColumnFormula>SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="558">
+    <tableColumn id="77" xr3:uid="{9872D8D3-B721-41DE-B43B-93F0D60E93F5}" name="Jugador" dataDxfId="483">
       <calculatedColumnFormula>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5382,7 +4857,7 @@
       </c>
       <c r="BX2" s="5">
         <f t="shared" ref="BX2:BX14" si="0">SUMPRODUCT((D2:BW2=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BY2" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5617,7 +5092,7 @@
       </c>
       <c r="BX3" s="5">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BY3" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -5852,7 +5327,7 @@
       </c>
       <c r="BX4" s="5">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="BY4" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6087,7 +5562,7 @@
       </c>
       <c r="BX5" s="5">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BY5" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6322,7 +5797,7 @@
       </c>
       <c r="BX6" s="5">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BY6" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6557,7 +6032,7 @@
       </c>
       <c r="BX7" s="5">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BY7" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -6792,7 +6267,7 @@
       </c>
       <c r="BX8" s="5">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="BY8" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -7027,7 +6502,7 @@
       </c>
       <c r="BX9" s="5">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="BY9" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -7262,7 +6737,7 @@
       </c>
       <c r="BX10" s="5">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BY10" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -7497,7 +6972,7 @@
       </c>
       <c r="BX11" s="5">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="BY11" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -7732,7 +7207,7 @@
       </c>
       <c r="BX12" s="5">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="BY12" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -7967,7 +7442,7 @@
       </c>
       <c r="BX13" s="5">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="BY13" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -8202,7 +7677,7 @@
       </c>
       <c r="BX14" s="5">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="BY14" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -8434,7 +7909,7 @@
       </c>
       <c r="BX15" s="5">
         <f>SUMPRODUCT((D15:BW15=D$18:BW$18)*(D$18:BW$18&lt;&gt;""))</f>
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BY15" t="str">
         <f>Form_Responses[[#This Row],[Aquí ponga su nombre y apellido]]</f>
@@ -8444,7 +7919,7 @@
     <row r="16" spans="1:77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="BX16" s="5"/>
     </row>
-    <row r="18" spans="1:73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>127</v>
       </c>
@@ -8622,6 +8097,12 @@
       <c r="BI18" s="7" t="s">
         <v>111</v>
       </c>
+      <c r="BJ18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="BK18" s="7" t="s">
+        <v>87</v>
+      </c>
       <c r="BL18" s="7" t="s">
         <v>76</v>
       </c>
@@ -8634,6 +8115,12 @@
       <c r="BO18" s="7" t="s">
         <v>89</v>
       </c>
+      <c r="BP18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="BQ18" s="7" t="s">
+        <v>124</v>
+      </c>
       <c r="BR18" s="7" t="s">
         <v>90</v>
       </c>
@@ -8644,338 +8131,374 @@
         <v>76</v>
       </c>
       <c r="BU18" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="BV18" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW18" s="7" t="s">
         <v>114</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D16">
-    <cfRule type="cellIs" dxfId="130" priority="66" operator="equal">
+    <cfRule type="cellIs" dxfId="142" priority="72" operator="equal">
       <formula>$D$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E16">
-    <cfRule type="cellIs" dxfId="129" priority="65" operator="equal">
+    <cfRule type="cellIs" dxfId="141" priority="71" operator="equal">
       <formula>$E$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F15">
-    <cfRule type="cellIs" dxfId="128" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="140" priority="48" operator="equal">
       <formula>$F$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G15">
-    <cfRule type="cellIs" dxfId="127" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="139" priority="45" operator="equal">
       <formula>$G$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H15">
-    <cfRule type="cellIs" dxfId="126" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="138" priority="20" operator="equal">
       <formula>$H$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I15">
-    <cfRule type="cellIs" dxfId="125" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="137" priority="19" operator="equal">
       <formula>$I$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J16">
-    <cfRule type="cellIs" dxfId="124" priority="64" operator="equal">
+    <cfRule type="cellIs" dxfId="136" priority="70" operator="equal">
       <formula>$J$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K15">
-    <cfRule type="cellIs" dxfId="123" priority="62" operator="equal">
+    <cfRule type="cellIs" dxfId="135" priority="68" operator="equal">
       <formula>$K$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L15">
-    <cfRule type="cellIs" dxfId="122" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="134" priority="47" operator="equal">
       <formula>$L$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M15">
-    <cfRule type="cellIs" dxfId="121" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="133" priority="46" operator="equal">
       <formula>$M$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N15">
-    <cfRule type="cellIs" dxfId="120" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="132" priority="24" operator="equal">
       <formula>$N$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O15">
-    <cfRule type="cellIs" dxfId="119" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="131" priority="23" operator="equal">
       <formula>$O$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P15">
-    <cfRule type="cellIs" dxfId="118" priority="61" operator="equal">
+    <cfRule type="cellIs" dxfId="130" priority="67" operator="equal">
       <formula>$P$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q15">
-    <cfRule type="cellIs" dxfId="117" priority="60" operator="equal">
+    <cfRule type="cellIs" dxfId="129" priority="66" operator="equal">
       <formula>$Q$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R15">
-    <cfRule type="cellIs" dxfId="116" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="128" priority="44" operator="equal">
       <formula>$R$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S15">
-    <cfRule type="cellIs" dxfId="115" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="127" priority="43" operator="equal">
       <formula>$S$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:T15">
-    <cfRule type="cellIs" dxfId="114" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="126" priority="22" operator="equal">
       <formula>$T$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U15">
-    <cfRule type="cellIs" dxfId="113" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="125" priority="21" operator="equal">
       <formula>$U$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V16">
-    <cfRule type="cellIs" dxfId="112" priority="63" operator="equal">
+    <cfRule type="cellIs" dxfId="124" priority="69" operator="equal">
       <formula>$V$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W15">
-    <cfRule type="cellIs" dxfId="111" priority="59" operator="equal">
+    <cfRule type="cellIs" dxfId="123" priority="65" operator="equal">
       <formula>$W$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X15">
-    <cfRule type="cellIs" dxfId="110" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="122" priority="42" operator="equal">
       <formula>$X$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y15">
-    <cfRule type="cellIs" dxfId="109" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="121" priority="41" operator="equal">
       <formula>$Y$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="Z2:Z15">
+    <cfRule type="cellIs" dxfId="120" priority="14" operator="equal">
+      <formula>$Z$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2:AA15">
+    <cfRule type="cellIs" dxfId="119" priority="13" operator="equal">
+      <formula>$AA$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB15">
-    <cfRule type="cellIs" dxfId="108" priority="58" operator="equal">
+    <cfRule type="cellIs" dxfId="118" priority="64" operator="equal">
       <formula>$AB$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC15">
-    <cfRule type="cellIs" dxfId="107" priority="56" operator="equal">
+    <cfRule type="cellIs" dxfId="117" priority="62" operator="equal">
       <formula>$AC$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD15">
-    <cfRule type="cellIs" dxfId="106" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="116" priority="40" operator="equal">
       <formula>$AD$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE15">
-    <cfRule type="cellIs" dxfId="105" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="115" priority="38" operator="equal">
       <formula>$AE$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF2:AF15">
-    <cfRule type="cellIs" dxfId="104" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="114" priority="18" operator="equal">
       <formula>$AF$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG2:AG15">
-    <cfRule type="cellIs" dxfId="103" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="113" priority="17" operator="equal">
       <formula>$AG$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH15">
-    <cfRule type="cellIs" dxfId="102" priority="57" operator="equal">
+    <cfRule type="cellIs" dxfId="112" priority="63" operator="equal">
       <formula>$AH$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI15">
-    <cfRule type="cellIs" dxfId="101" priority="55" operator="equal">
+    <cfRule type="cellIs" dxfId="111" priority="61" operator="equal">
       <formula>$AI$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ2:AJ15">
-    <cfRule type="cellIs" dxfId="100" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="110" priority="39" operator="equal">
       <formula>$AJ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK2:AK15">
-    <cfRule type="cellIs" dxfId="99" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="109" priority="37" operator="equal">
       <formula>$AK$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL2:AL15">
-    <cfRule type="cellIs" dxfId="98" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="108" priority="16" operator="equal">
       <formula>$AL$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM2:AM15">
-    <cfRule type="cellIs" dxfId="97" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="107" priority="15" operator="equal">
       <formula>$AM$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN15">
-    <cfRule type="cellIs" dxfId="96" priority="52" operator="equal">
+    <cfRule type="cellIs" dxfId="106" priority="58" operator="equal">
       <formula>$AN$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO2:AO15">
-    <cfRule type="cellIs" dxfId="95" priority="51" operator="equal">
+    <cfRule type="cellIs" dxfId="105" priority="57" operator="equal">
       <formula>$AO$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP2:AP15">
-    <cfRule type="cellIs" dxfId="94" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="104" priority="34" operator="equal">
       <formula>$AP$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ2:AQ15">
-    <cfRule type="cellIs" dxfId="93" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="103" priority="33" operator="equal">
       <formula>$AQ$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AR2:AR15">
+    <cfRule type="cellIs" dxfId="102" priority="12" operator="equal">
+      <formula>$AR$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AS2:AS15">
+    <cfRule type="cellIs" dxfId="101" priority="11" operator="equal">
+      <formula>$AS$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT15">
-    <cfRule type="cellIs" dxfId="92" priority="54" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="60" operator="equal">
       <formula>$AT$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU2:AU15">
-    <cfRule type="cellIs" dxfId="91" priority="53" operator="equal">
+    <cfRule type="cellIs" dxfId="99" priority="59" operator="equal">
       <formula>$AU$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV2:AV15">
-    <cfRule type="cellIs" dxfId="90" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="98" priority="36" operator="equal">
       <formula>$AV$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW2:AW15">
-    <cfRule type="cellIs" dxfId="89" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="97" priority="35" operator="equal">
       <formula>$AW$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AX2:AX16">
+    <cfRule type="cellIs" dxfId="96" priority="9" operator="equal">
+      <formula>$AX$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AY2:AY15">
+    <cfRule type="cellIs" dxfId="95" priority="10" operator="equal">
+      <formula>$AY$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AZ2:AZ15">
-    <cfRule type="cellIs" dxfId="88" priority="50" operator="equal">
+    <cfRule type="cellIs" dxfId="94" priority="56" operator="equal">
       <formula>$AZ$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA2:BA15">
-    <cfRule type="cellIs" dxfId="87" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="55" operator="equal">
       <formula>$BA$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB2:BB15">
-    <cfRule type="cellIs" dxfId="86" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="31" operator="equal">
       <formula>$BB$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BC2:BC15">
-    <cfRule type="cellIs" dxfId="85" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="30" operator="equal">
       <formula>$BC$18</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="BD2:BD15">
+    <cfRule type="cellIs" dxfId="90" priority="8" operator="equal">
+      <formula>$BD$18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BE2:BE15">
+    <cfRule type="cellIs" dxfId="89" priority="7" operator="equal">
+      <formula>$BE$18</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="BF2:BF15">
-    <cfRule type="cellIs" dxfId="84" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="88" priority="54" operator="equal">
       <formula>$BF$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BG2:BG15">
-    <cfRule type="cellIs" dxfId="83" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="53" operator="equal">
       <formula>$BG$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BH2:BH15">
-    <cfRule type="cellIs" dxfId="82" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="32" operator="equal">
       <formula>$BH$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI2:BI15">
-    <cfRule type="cellIs" dxfId="81" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="26" operator="equal">
       <formula>$BI$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL2:BL15">
-    <cfRule type="cellIs" dxfId="80" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="52" operator="equal">
       <formula>$BL$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM2:BM15">
-    <cfRule type="cellIs" dxfId="79" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="49" operator="equal">
       <formula>$BM$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BN2:BN15">
-    <cfRule type="cellIs" dxfId="78" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="27" operator="equal">
       <formula>$BN$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BO2:BO15">
-    <cfRule type="cellIs" dxfId="77" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="25" operator="equal">
       <formula>$BO$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BR2:BR15">
-    <cfRule type="cellIs" dxfId="76" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="51" operator="equal">
       <formula>$BR$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS2:BS15">
-    <cfRule type="cellIs" dxfId="75" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="50" operator="equal">
       <formula>$BS$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BT2:BT15">
-    <cfRule type="cellIs" dxfId="74" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="29" operator="equal">
       <formula>$BT$18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BU2:BU15">
-    <cfRule type="cellIs" dxfId="73" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="28" operator="equal">
       <formula>$BU$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z2:Z15">
-    <cfRule type="cellIs" dxfId="72" priority="8" operator="equal">
-      <formula>$Z$18</formula>
+  <conditionalFormatting sqref="BV2:BV15">
+    <cfRule type="cellIs" dxfId="76" priority="6" operator="equal">
+      <formula>$BV$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA15">
-    <cfRule type="cellIs" dxfId="71" priority="7" operator="equal">
-      <formula>$AA$18</formula>
+  <conditionalFormatting sqref="BW2:BW15">
+    <cfRule type="cellIs" dxfId="75" priority="5" operator="equal">
+      <formula>$BW$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AR2:AR15">
-    <cfRule type="cellIs" dxfId="70" priority="6" operator="equal">
-      <formula>$AR$18</formula>
+  <conditionalFormatting sqref="BP2:BP15">
+    <cfRule type="cellIs" dxfId="74" priority="4" operator="equal">
+      <formula>$BP$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AS2:AS15">
-    <cfRule type="cellIs" dxfId="69" priority="5" operator="equal">
-      <formula>$AS$18</formula>
+  <conditionalFormatting sqref="BQ2:BQ15">
+    <cfRule type="cellIs" dxfId="73" priority="3" operator="equal">
+      <formula>$BQ$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AY2:AY15">
-    <cfRule type="cellIs" dxfId="68" priority="4" operator="equal">
-      <formula>$AY$18</formula>
+  <conditionalFormatting sqref="BJ2:BJ15">
+    <cfRule type="cellIs" dxfId="72" priority="2" operator="equal">
+      <formula>$BJ$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AX2:AX16">
-    <cfRule type="cellIs" dxfId="67" priority="3" operator="equal">
-      <formula>$AX$18</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BD2:BD15">
-    <cfRule type="cellIs" dxfId="66" priority="2" operator="equal">
-      <formula>$BD$18</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BE2:BE15">
+  <conditionalFormatting sqref="BK2:BK15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$BE$18</formula>
+      <formula>$BK$18</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
